--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\gcloud\projs\fumarate\src\test\java\gbench\sandbox\mall\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9CC60A-D922-4AE7-8D82-46B5F467C4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBADF8A-2D53-467B-917A-52828826A353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_company" sheetId="1" r:id="rId1"/>
@@ -22,26 +22,17 @@
     <sheet name="t_journal" sheetId="8" r:id="rId7"/>
     <sheet name="t_bksys" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="1436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="1475">
   <si>
     <t>Walmart</t>
   </si>
@@ -3354,10 +3345,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>category</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4784,6 +4771,127 @@
   <si>
     <t>due_date</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.72}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.73}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.74}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.75}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.76}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.77}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.78}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.79}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.80}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.81}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.82}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.83}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.84}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.85}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.86}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.87}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.88}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.89}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.90}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.91}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.92}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.93}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.94}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.95}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.96}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.97}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.98}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.99}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.100}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.101}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.102}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.103}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.104}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.105}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.106}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.107}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.108}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.109}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.110}</t>
+  </si>
+  <si>
+    <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.111}</t>
   </si>
 </sst>
 </file>
@@ -10688,7 +10796,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="D2" t="s">
         <v>1003</v>
@@ -10868,7 +10976,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="D11" t="s">
         <v>1034</v>
@@ -10944,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>1077</v>
+        <v>1435</v>
       </c>
       <c r="F2" s="2">
         <v>45072.29583333333</v>
@@ -10964,7 +11072,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>1077</v>
+        <v>1436</v>
       </c>
       <c r="F3" s="2">
         <v>45072.29583333333</v>
@@ -10984,7 +11092,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>1077</v>
+        <v>1437</v>
       </c>
       <c r="F4" s="2">
         <v>45072.29583333333</v>
@@ -11004,7 +11112,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>1077</v>
+        <v>1438</v>
       </c>
       <c r="F5" s="2">
         <v>45072.29583333333</v>
@@ -11024,7 +11132,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>1077</v>
+        <v>1439</v>
       </c>
       <c r="F6" s="2">
         <v>45072.29583333333</v>
@@ -11044,7 +11152,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>1077</v>
+        <v>1440</v>
       </c>
       <c r="F7" s="2">
         <v>45072.29583333333</v>
@@ -11064,7 +11172,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>1077</v>
+        <v>1441</v>
       </c>
       <c r="F8" s="2">
         <v>45072.29583333333</v>
@@ -11084,7 +11192,7 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>1077</v>
+        <v>1442</v>
       </c>
       <c r="F9" s="2">
         <v>45072.29583333333</v>
@@ -11104,7 +11212,7 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>1077</v>
+        <v>1443</v>
       </c>
       <c r="F10" s="2">
         <v>45072.29583333333</v>
@@ -11124,7 +11232,7 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>1077</v>
+        <v>1444</v>
       </c>
       <c r="F11" s="2">
         <v>45072.29583333333</v>
@@ -11144,7 +11252,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>1077</v>
+        <v>1445</v>
       </c>
       <c r="F12" s="2">
         <v>45072.29583333333</v>
@@ -11164,7 +11272,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>1077</v>
+        <v>1446</v>
       </c>
       <c r="F13" s="2">
         <v>45072.29583333333</v>
@@ -11184,7 +11292,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>1077</v>
+        <v>1447</v>
       </c>
       <c r="F14" s="2">
         <v>45072.29583333333</v>
@@ -11204,7 +11312,7 @@
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>1077</v>
+        <v>1448</v>
       </c>
       <c r="F15" s="2">
         <v>45072.29583333333</v>
@@ -11224,7 +11332,7 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>1077</v>
+        <v>1449</v>
       </c>
       <c r="F16" s="2">
         <v>45072.29583333333</v>
@@ -11244,7 +11352,7 @@
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>1077</v>
+        <v>1450</v>
       </c>
       <c r="F17" s="2">
         <v>45072.29583333333</v>
@@ -11264,7 +11372,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>1077</v>
+        <v>1451</v>
       </c>
       <c r="F18" s="2">
         <v>45072.29583333333</v>
@@ -11284,7 +11392,7 @@
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>1077</v>
+        <v>1452</v>
       </c>
       <c r="F19" s="2">
         <v>45072.29583333333</v>
@@ -11304,7 +11412,7 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>1077</v>
+        <v>1453</v>
       </c>
       <c r="F20" s="2">
         <v>45072.29583333333</v>
@@ -11324,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>1077</v>
+        <v>1454</v>
       </c>
       <c r="F21" s="2">
         <v>45072.29583333333</v>
@@ -11344,7 +11452,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>1077</v>
+        <v>1455</v>
       </c>
       <c r="F22" s="2">
         <v>45072.29583333333</v>
@@ -11364,7 +11472,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>1077</v>
+        <v>1456</v>
       </c>
       <c r="F23" s="2">
         <v>45072.29583333333</v>
@@ -11384,7 +11492,7 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>1077</v>
+        <v>1457</v>
       </c>
       <c r="F24" s="2">
         <v>45072.29583333333</v>
@@ -11404,7 +11512,7 @@
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>1077</v>
+        <v>1458</v>
       </c>
       <c r="F25" s="2">
         <v>45072.29583333333</v>
@@ -11424,7 +11532,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>1077</v>
+        <v>1459</v>
       </c>
       <c r="F26" s="2">
         <v>45072.29583333333</v>
@@ -11444,7 +11552,7 @@
         <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>1077</v>
+        <v>1460</v>
       </c>
       <c r="F27" s="2">
         <v>45072.29583333333</v>
@@ -11464,7 +11572,7 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>1077</v>
+        <v>1461</v>
       </c>
       <c r="F28" s="2">
         <v>45072.29583333333</v>
@@ -11484,7 +11592,7 @@
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>1077</v>
+        <v>1462</v>
       </c>
       <c r="F29" s="2">
         <v>45072.29583333333</v>
@@ -11504,7 +11612,7 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>1077</v>
+        <v>1463</v>
       </c>
       <c r="F30" s="2">
         <v>45072.29583333333</v>
@@ -11524,7 +11632,7 @@
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>1077</v>
+        <v>1464</v>
       </c>
       <c r="F31" s="2">
         <v>45072.29583333333</v>
@@ -11544,7 +11652,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>1077</v>
+        <v>1465</v>
       </c>
       <c r="F32" s="2">
         <v>45072.29583333333</v>
@@ -11564,7 +11672,7 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>1077</v>
+        <v>1466</v>
       </c>
       <c r="F33" s="2">
         <v>45072.29583333333</v>
@@ -11584,7 +11692,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>1077</v>
+        <v>1467</v>
       </c>
       <c r="F34" s="2">
         <v>45072.29583333333</v>
@@ -11604,7 +11712,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>1077</v>
+        <v>1468</v>
       </c>
       <c r="F35" s="2">
         <v>45072.29583333333</v>
@@ -11624,7 +11732,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>1077</v>
+        <v>1469</v>
       </c>
       <c r="F36" s="2">
         <v>45072.29583333333</v>
@@ -11644,7 +11752,7 @@
         <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>1077</v>
+        <v>1470</v>
       </c>
       <c r="F37" s="2">
         <v>45072.29583333333</v>
@@ -11664,7 +11772,7 @@
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>1077</v>
+        <v>1471</v>
       </c>
       <c r="F38" s="2">
         <v>45072.29583333333</v>
@@ -11684,7 +11792,7 @@
         <v>8</v>
       </c>
       <c r="E39" t="s">
-        <v>1077</v>
+        <v>1472</v>
       </c>
       <c r="F39" s="2">
         <v>45072.29583333333</v>
@@ -11704,7 +11812,7 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>1077</v>
+        <v>1473</v>
       </c>
       <c r="F40" s="2">
         <v>45072.29583333333</v>
@@ -11724,7 +11832,7 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>1077</v>
+        <v>1474</v>
       </c>
       <c r="F41" s="2">
         <v>45072.29583333333</v>
@@ -11785,7 +11893,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>37815.26106557616</v>
+        <v>39376.176381075384</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11810,7 +11918,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>42488.999133253186</v>
+        <v>37446.542880537068</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -11835,7 +11943,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35453.714504273805</v>
+        <v>36411.541339806747</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -11860,7 +11968,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>45097.407743763884</v>
+        <v>37021.343457043185</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -11885,7 +11993,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42814.735994009061</v>
+        <v>41862.780972037763</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -11910,7 +12018,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44432.987991276452</v>
+        <v>41141.331984896715</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -11935,7 +12043,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37477.93147999105</v>
+        <v>40737.584973109711</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -11960,7 +12068,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36118.818042807572</v>
+        <v>36663.822738185001</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -11985,7 +12093,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44278.918550190901</v>
+        <v>36054.873660656966</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12010,7 +12118,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42865.592925972094</v>
+        <v>40677.37141947019</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12035,7 +12143,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39102.327133066974</v>
+        <v>42570.500409609078</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12060,7 +12168,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42315.216669271962</v>
+        <v>44579.374396718056</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12085,7 +12193,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38128.772904410122</v>
+        <v>42930.657935193303</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12110,7 +12218,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41453.077151769445</v>
+        <v>43225.462032391471</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12135,7 +12243,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44921.206564632317</v>
+        <v>43771.078392757445</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12160,7 +12268,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41171.98945776539</v>
+        <v>44624.689090226995</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12185,7 +12293,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44957.066744095704</v>
+        <v>44272.827548197449</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12210,7 +12318,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38027.260058839682</v>
+        <v>39874.041318655887</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12235,7 +12343,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37845.58942118947</v>
+        <v>38644.721966224562</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12260,7 +12368,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38729.661026259018</v>
+        <v>37349.220562157818</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12285,7 +12393,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44947.47729881743</v>
+        <v>41892.460311830037</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12310,7 +12418,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41580.380754439808</v>
+        <v>36414.469033721878</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12335,7 +12443,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35959.813491305969</v>
+        <v>41755.736868250904</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12360,7 +12468,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39998.97271066298</v>
+        <v>43691.602923708924</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12385,7 +12493,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36096.106978061915</v>
+        <v>38111.033206565167</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12410,7 +12518,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35823.892209011436</v>
+        <v>44441.420961858552</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12435,7 +12543,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44802.196869760228</v>
+        <v>38582.446778760786</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12460,7 +12568,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38787.813234996895</v>
+        <v>36952.703192369343</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12485,7 +12593,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43800.025439673147</v>
+        <v>39033.0432240265</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12510,7 +12618,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38472.666977268542</v>
+        <v>37366.423738125617</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -12552,19 +12660,19 @@
         <v>998</v>
       </c>
       <c r="D2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="E2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="F2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="H2" t="s">
         <v>1078</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1423</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.2">
@@ -12572,19 +12680,19 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E3" t="s">
         <v>1080</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>1081</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1082</v>
       </c>
       <c r="G3">
         <v>1001</v>
       </c>
       <c r="H3" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.2">
@@ -12592,19 +12700,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E4" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="F4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G4">
         <v>1002</v>
       </c>
       <c r="H4" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.2">
@@ -12612,19 +12720,19 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E5" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="F5" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G5">
         <v>1003</v>
       </c>
       <c r="H5" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.2">
@@ -12632,19 +12740,19 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E6" t="s">
         <v>1086</v>
       </c>
-      <c r="E6" t="s">
-        <v>1087</v>
-      </c>
       <c r="F6" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G6">
         <v>1011</v>
       </c>
       <c r="H6" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.2">
@@ -12652,19 +12760,19 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E7" t="s">
         <v>1088</v>
       </c>
-      <c r="E7" t="s">
-        <v>1089</v>
-      </c>
       <c r="F7" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G7">
         <v>1015</v>
       </c>
       <c r="H7" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.2">
@@ -12672,19 +12780,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E8" t="s">
         <v>1090</v>
       </c>
-      <c r="E8" t="s">
-        <v>1091</v>
-      </c>
       <c r="F8" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G8">
         <v>1021</v>
       </c>
       <c r="H8" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.2">
@@ -12692,19 +12800,19 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E9" t="s">
         <v>1093</v>
       </c>
-      <c r="E9" t="s">
-        <v>1094</v>
-      </c>
       <c r="F9" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G9">
         <v>1031</v>
       </c>
       <c r="H9" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.2">
@@ -12712,19 +12820,19 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E10" t="s">
         <v>1096</v>
       </c>
-      <c r="E10" t="s">
-        <v>1097</v>
-      </c>
       <c r="F10" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G10">
         <v>1051</v>
       </c>
       <c r="H10" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.2">
@@ -12732,19 +12840,19 @@
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E11" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="F11" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G11">
         <v>1101</v>
       </c>
       <c r="H11" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.2">
@@ -12752,19 +12860,19 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E12" t="s">
         <v>1099</v>
       </c>
-      <c r="E12" t="s">
-        <v>1100</v>
-      </c>
       <c r="F12" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G12">
         <v>1111</v>
       </c>
       <c r="H12" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.2">
@@ -12772,19 +12880,19 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E13" t="s">
         <v>1101</v>
       </c>
-      <c r="E13" t="s">
-        <v>1102</v>
-      </c>
       <c r="F13" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G13">
         <v>1121</v>
       </c>
       <c r="H13" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.2">
@@ -12792,19 +12900,19 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E14" t="s">
         <v>1103</v>
       </c>
-      <c r="E14" t="s">
-        <v>1104</v>
-      </c>
       <c r="F14" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G14">
         <v>1122</v>
       </c>
       <c r="H14" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="15" spans="3:8" x14ac:dyDescent="0.2">
@@ -12812,19 +12920,19 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E15" t="s">
         <v>1105</v>
       </c>
-      <c r="E15" t="s">
-        <v>1106</v>
-      </c>
       <c r="F15" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G15">
         <v>1123</v>
       </c>
       <c r="H15" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="16" spans="3:8" x14ac:dyDescent="0.2">
@@ -12832,19 +12940,19 @@
         <v>14</v>
       </c>
       <c r="D16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E16" t="s">
         <v>1107</v>
       </c>
-      <c r="E16" t="s">
-        <v>1108</v>
-      </c>
       <c r="F16" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G16">
         <v>1131</v>
       </c>
       <c r="H16" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.2">
@@ -12852,19 +12960,19 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E17" t="s">
         <v>1109</v>
       </c>
-      <c r="E17" t="s">
-        <v>1110</v>
-      </c>
       <c r="F17" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G17">
         <v>1132</v>
       </c>
       <c r="H17" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.2">
@@ -12872,19 +12980,19 @@
         <v>16</v>
       </c>
       <c r="D18" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E18" t="s">
         <v>1111</v>
       </c>
-      <c r="E18" t="s">
-        <v>1112</v>
-      </c>
       <c r="F18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G18">
         <v>1211</v>
       </c>
       <c r="H18" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.2">
@@ -12892,19 +13000,19 @@
         <v>17</v>
       </c>
       <c r="D19" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E19" t="s">
         <v>1114</v>
       </c>
-      <c r="E19" t="s">
-        <v>1115</v>
-      </c>
       <c r="F19" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G19">
         <v>1221</v>
       </c>
       <c r="H19" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.2">
@@ -12912,19 +13020,19 @@
         <v>18</v>
       </c>
       <c r="D20" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E20" t="s">
         <v>1116</v>
       </c>
-      <c r="E20" t="s">
-        <v>1117</v>
-      </c>
       <c r="F20" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G20">
         <v>1222</v>
       </c>
       <c r="H20" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="21" spans="3:8" x14ac:dyDescent="0.2">
@@ -12932,19 +13040,19 @@
         <v>19</v>
       </c>
       <c r="D21" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E21" t="s">
         <v>1118</v>
       </c>
-      <c r="E21" t="s">
-        <v>1119</v>
-      </c>
       <c r="F21" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G21">
         <v>1223</v>
       </c>
       <c r="H21" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.2">
@@ -12952,19 +13060,19 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E22" t="s">
         <v>1120</v>
       </c>
-      <c r="E22" t="s">
-        <v>1121</v>
-      </c>
       <c r="F22" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G22">
         <v>1224</v>
       </c>
       <c r="H22" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.2">
@@ -12972,19 +13080,19 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E23" t="s">
         <v>1122</v>
       </c>
-      <c r="E23" t="s">
-        <v>1123</v>
-      </c>
       <c r="F23" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G23">
         <v>1231</v>
       </c>
       <c r="H23" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.2">
@@ -12992,19 +13100,19 @@
         <v>22</v>
       </c>
       <c r="D24" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E24" t="s">
         <v>1124</v>
       </c>
-      <c r="E24" t="s">
-        <v>1125</v>
-      </c>
       <c r="F24" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G24">
         <v>1241</v>
       </c>
       <c r="H24" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.2">
@@ -13012,19 +13120,19 @@
         <v>23</v>
       </c>
       <c r="D25" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E25" t="s">
         <v>1126</v>
       </c>
-      <c r="E25" t="s">
-        <v>1127</v>
-      </c>
       <c r="F25" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G25">
         <v>1251</v>
       </c>
       <c r="H25" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.2">
@@ -13032,19 +13140,19 @@
         <v>24</v>
       </c>
       <c r="D26" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E26" t="s">
         <v>1128</v>
       </c>
-      <c r="E26" t="s">
-        <v>1129</v>
-      </c>
       <c r="F26" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G26">
         <v>1301</v>
       </c>
       <c r="H26" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.2">
@@ -13052,19 +13160,19 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E27" t="s">
         <v>1131</v>
       </c>
-      <c r="E27" t="s">
-        <v>1132</v>
-      </c>
       <c r="F27" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G27">
         <v>1302</v>
       </c>
       <c r="H27" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.2">
@@ -13072,19 +13180,19 @@
         <v>26</v>
       </c>
       <c r="D28" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E28" t="s">
         <v>1133</v>
       </c>
-      <c r="E28" t="s">
-        <v>1134</v>
-      </c>
       <c r="F28" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G28">
         <v>1311</v>
       </c>
       <c r="H28" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.2">
@@ -13092,19 +13200,19 @@
         <v>27</v>
       </c>
       <c r="D29" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E29" t="s">
         <v>1135</v>
       </c>
-      <c r="E29" t="s">
-        <v>1136</v>
-      </c>
       <c r="F29" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G29">
         <v>1321</v>
       </c>
       <c r="H29" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.2">
@@ -13112,19 +13220,19 @@
         <v>28</v>
       </c>
       <c r="D30" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E30" t="s">
         <v>1137</v>
       </c>
-      <c r="E30" t="s">
-        <v>1138</v>
-      </c>
       <c r="F30" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G30">
         <v>1401</v>
       </c>
       <c r="H30" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.2">
@@ -13132,19 +13240,19 @@
         <v>29</v>
       </c>
       <c r="D31" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E31" t="s">
         <v>1139</v>
       </c>
-      <c r="E31" t="s">
-        <v>1140</v>
-      </c>
       <c r="F31" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G31">
         <v>1402</v>
       </c>
       <c r="H31" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.2">
@@ -13152,19 +13260,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E32" t="s">
         <v>1141</v>
       </c>
-      <c r="E32" t="s">
-        <v>1142</v>
-      </c>
       <c r="F32" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G32">
         <v>1403</v>
       </c>
       <c r="H32" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.2">
@@ -13172,19 +13280,19 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E33" t="s">
         <v>1143</v>
       </c>
-      <c r="E33" t="s">
-        <v>1144</v>
-      </c>
       <c r="F33" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G33">
         <v>1404</v>
       </c>
       <c r="H33" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.2">
@@ -13192,19 +13300,19 @@
         <v>32</v>
       </c>
       <c r="D34" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E34" t="s">
         <v>1145</v>
       </c>
-      <c r="E34" t="s">
-        <v>1146</v>
-      </c>
       <c r="F34" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G34">
         <v>1406</v>
       </c>
       <c r="H34" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.2">
@@ -13212,19 +13320,19 @@
         <v>33</v>
       </c>
       <c r="D35" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E35" t="s">
         <v>1147</v>
       </c>
-      <c r="E35" t="s">
-        <v>1148</v>
-      </c>
       <c r="F35" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G35">
         <v>1407</v>
       </c>
       <c r="H35" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.2">
@@ -13232,19 +13340,19 @@
         <v>34</v>
       </c>
       <c r="D36" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E36" t="s">
         <v>1149</v>
       </c>
-      <c r="E36" t="s">
-        <v>1150</v>
-      </c>
       <c r="F36" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G36">
         <v>1410</v>
       </c>
       <c r="H36" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.2">
@@ -13252,19 +13360,19 @@
         <v>35</v>
       </c>
       <c r="D37" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E37" t="s">
         <v>1151</v>
       </c>
-      <c r="E37" t="s">
-        <v>1152</v>
-      </c>
       <c r="F37" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G37">
         <v>1411</v>
       </c>
       <c r="H37" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.2">
@@ -13272,19 +13380,19 @@
         <v>36</v>
       </c>
       <c r="D38" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E38" t="s">
         <v>1153</v>
       </c>
-      <c r="E38" t="s">
-        <v>1154</v>
-      </c>
       <c r="F38" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G38">
         <v>1412</v>
       </c>
       <c r="H38" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.2">
@@ -13292,19 +13400,19 @@
         <v>37</v>
       </c>
       <c r="D39" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E39" t="s">
         <v>1155</v>
       </c>
-      <c r="E39" t="s">
-        <v>1156</v>
-      </c>
       <c r="F39" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G39">
         <v>1421</v>
       </c>
       <c r="H39" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.2">
@@ -13312,19 +13420,19 @@
         <v>38</v>
       </c>
       <c r="D40" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E40" t="s">
         <v>1158</v>
       </c>
-      <c r="E40" t="s">
-        <v>1159</v>
-      </c>
       <c r="F40" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G40">
         <v>1431</v>
       </c>
       <c r="H40" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.2">
@@ -13332,19 +13440,19 @@
         <v>39</v>
       </c>
       <c r="D41" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E41" t="s">
         <v>1161</v>
       </c>
-      <c r="E41" t="s">
-        <v>1162</v>
-      </c>
       <c r="F41" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G41">
         <v>1441</v>
       </c>
       <c r="H41" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.2">
@@ -13352,19 +13460,19 @@
         <v>40</v>
       </c>
       <c r="D42" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E42" t="s">
         <v>1163</v>
       </c>
-      <c r="E42" t="s">
-        <v>1164</v>
-      </c>
       <c r="F42" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G42">
         <v>1442</v>
       </c>
       <c r="H42" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="43" spans="3:8" x14ac:dyDescent="0.2">
@@ -13372,19 +13480,19 @@
         <v>41</v>
       </c>
       <c r="D43" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E43" t="s">
         <v>1165</v>
       </c>
-      <c r="E43" t="s">
-        <v>1166</v>
-      </c>
       <c r="F43" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G43">
         <v>1451</v>
       </c>
       <c r="H43" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.2">
@@ -13392,19 +13500,19 @@
         <v>42</v>
       </c>
       <c r="D44" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E44" t="s">
         <v>1167</v>
       </c>
-      <c r="E44" t="s">
-        <v>1168</v>
-      </c>
       <c r="F44" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G44">
         <v>1461</v>
       </c>
       <c r="H44" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.2">
@@ -13412,19 +13520,19 @@
         <v>43</v>
       </c>
       <c r="D45" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E45" t="s">
         <v>1169</v>
       </c>
-      <c r="E45" t="s">
-        <v>1170</v>
-      </c>
       <c r="F45" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G45">
         <v>1511</v>
       </c>
       <c r="H45" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.2">
@@ -13432,19 +13540,19 @@
         <v>44</v>
       </c>
       <c r="D46" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E46" t="s">
         <v>1171</v>
       </c>
-      <c r="E46" t="s">
-        <v>1172</v>
-      </c>
       <c r="F46" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G46">
         <v>1521</v>
       </c>
       <c r="H46" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="47" spans="3:8" x14ac:dyDescent="0.2">
@@ -13452,19 +13560,19 @@
         <v>45</v>
       </c>
       <c r="D47" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E47" t="s">
         <v>1173</v>
       </c>
-      <c r="E47" t="s">
-        <v>1174</v>
-      </c>
       <c r="F47" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G47">
         <v>1522</v>
       </c>
       <c r="H47" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.2">
@@ -13472,19 +13580,19 @@
         <v>46</v>
       </c>
       <c r="D48" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E48" t="s">
         <v>1175</v>
       </c>
-      <c r="E48" t="s">
-        <v>1176</v>
-      </c>
       <c r="F48" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G48">
         <v>1523</v>
       </c>
       <c r="H48" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.2">
@@ -13492,19 +13600,19 @@
         <v>47</v>
       </c>
       <c r="D49" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E49" t="s">
         <v>1177</v>
       </c>
-      <c r="E49" t="s">
-        <v>1178</v>
-      </c>
       <c r="F49" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G49">
         <v>1524</v>
       </c>
       <c r="H49" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.2">
@@ -13512,19 +13620,19 @@
         <v>48</v>
       </c>
       <c r="D50" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E50" t="s">
         <v>1179</v>
       </c>
-      <c r="E50" t="s">
-        <v>1180</v>
-      </c>
       <c r="F50" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G50">
         <v>1525</v>
       </c>
       <c r="H50" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.2">
@@ -13532,19 +13640,19 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E51" t="s">
         <v>1181</v>
       </c>
-      <c r="E51" t="s">
-        <v>1182</v>
-      </c>
       <c r="F51" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G51">
         <v>1526</v>
       </c>
       <c r="H51" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.2">
@@ -13552,19 +13660,19 @@
         <v>50</v>
       </c>
       <c r="D52" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E52" t="s">
         <v>1183</v>
       </c>
-      <c r="E52" t="s">
-        <v>1184</v>
-      </c>
       <c r="F52" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G52">
         <v>1531</v>
       </c>
       <c r="H52" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="53" spans="3:8" x14ac:dyDescent="0.2">
@@ -13572,19 +13680,19 @@
         <v>51</v>
       </c>
       <c r="D53" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E53" t="s">
         <v>1185</v>
       </c>
-      <c r="E53" t="s">
-        <v>1186</v>
-      </c>
       <c r="F53" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G53">
         <v>1541</v>
       </c>
       <c r="H53" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.2">
@@ -13592,19 +13700,19 @@
         <v>52</v>
       </c>
       <c r="D54" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E54" t="s">
         <v>1187</v>
       </c>
-      <c r="E54" t="s">
-        <v>1188</v>
-      </c>
       <c r="F54" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G54">
         <v>1551</v>
       </c>
       <c r="H54" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.2">
@@ -13612,19 +13720,19 @@
         <v>53</v>
       </c>
       <c r="D55" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E55" t="s">
         <v>1189</v>
       </c>
-      <c r="E55" t="s">
-        <v>1190</v>
-      </c>
       <c r="F55" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G55">
         <v>1601</v>
       </c>
       <c r="H55" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.2">
@@ -13632,19 +13740,19 @@
         <v>54</v>
       </c>
       <c r="D56" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E56" t="s">
         <v>1191</v>
       </c>
-      <c r="E56" t="s">
-        <v>1192</v>
-      </c>
       <c r="F56" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G56">
         <v>1602</v>
       </c>
       <c r="H56" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.2">
@@ -13652,19 +13760,19 @@
         <v>55</v>
       </c>
       <c r="D57" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E57" t="s">
         <v>1193</v>
       </c>
-      <c r="E57" t="s">
-        <v>1194</v>
-      </c>
       <c r="F57" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G57">
         <v>1603</v>
       </c>
       <c r="H57" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.2">
@@ -13672,19 +13780,19 @@
         <v>56</v>
       </c>
       <c r="D58" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E58" t="s">
         <v>1195</v>
       </c>
-      <c r="E58" t="s">
-        <v>1196</v>
-      </c>
       <c r="F58" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G58">
         <v>1604</v>
       </c>
       <c r="H58" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.2">
@@ -13692,19 +13800,19 @@
         <v>57</v>
       </c>
       <c r="D59" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E59" t="s">
         <v>1197</v>
       </c>
-      <c r="E59" t="s">
-        <v>1198</v>
-      </c>
       <c r="F59" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G59">
         <v>1605</v>
       </c>
       <c r="H59" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="60" spans="3:8" x14ac:dyDescent="0.2">
@@ -13712,19 +13820,19 @@
         <v>58</v>
       </c>
       <c r="D60" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E60" t="s">
         <v>1199</v>
       </c>
-      <c r="E60" t="s">
-        <v>1200</v>
-      </c>
       <c r="F60" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G60">
         <v>1606</v>
       </c>
       <c r="H60" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.2">
@@ -13732,19 +13840,19 @@
         <v>59</v>
       </c>
       <c r="D61" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E61" t="s">
         <v>1201</v>
       </c>
-      <c r="E61" t="s">
-        <v>1202</v>
-      </c>
       <c r="F61" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G61">
         <v>1611</v>
       </c>
       <c r="H61" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="62" spans="3:8" x14ac:dyDescent="0.2">
@@ -13752,19 +13860,19 @@
         <v>60</v>
       </c>
       <c r="D62" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E62" t="s">
         <v>1204</v>
       </c>
-      <c r="E62" t="s">
-        <v>1205</v>
-      </c>
       <c r="F62" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G62">
         <v>1612</v>
       </c>
       <c r="H62" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="63" spans="3:8" x14ac:dyDescent="0.2">
@@ -13772,19 +13880,19 @@
         <v>61</v>
       </c>
       <c r="D63" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E63" t="s">
         <v>1206</v>
       </c>
-      <c r="E63" t="s">
-        <v>1207</v>
-      </c>
       <c r="F63" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G63">
         <v>1621</v>
       </c>
       <c r="H63" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="64" spans="3:8" x14ac:dyDescent="0.2">
@@ -13792,19 +13900,19 @@
         <v>62</v>
       </c>
       <c r="D64" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E64" t="s">
         <v>1208</v>
       </c>
-      <c r="E64" t="s">
-        <v>1209</v>
-      </c>
       <c r="F64" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G64">
         <v>1622</v>
       </c>
       <c r="H64" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="65" spans="3:8" x14ac:dyDescent="0.2">
@@ -13812,19 +13920,19 @@
         <v>63</v>
       </c>
       <c r="D65" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E65" t="s">
         <v>1210</v>
       </c>
-      <c r="E65" t="s">
-        <v>1211</v>
-      </c>
       <c r="F65" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G65">
         <v>1623</v>
       </c>
       <c r="H65" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="66" spans="3:8" x14ac:dyDescent="0.2">
@@ -13832,19 +13940,19 @@
         <v>64</v>
       </c>
       <c r="D66" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E66" t="s">
         <v>1212</v>
       </c>
-      <c r="E66" t="s">
-        <v>1213</v>
-      </c>
       <c r="F66" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G66">
         <v>1631</v>
       </c>
       <c r="H66" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="67" spans="3:8" x14ac:dyDescent="0.2">
@@ -13852,19 +13960,19 @@
         <v>65</v>
       </c>
       <c r="D67" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E67" t="s">
         <v>1215</v>
       </c>
-      <c r="E67" t="s">
-        <v>1216</v>
-      </c>
       <c r="F67" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G67">
         <v>1632</v>
       </c>
       <c r="H67" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="68" spans="3:8" x14ac:dyDescent="0.2">
@@ -13872,19 +13980,19 @@
         <v>66</v>
       </c>
       <c r="D68" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E68" t="s">
         <v>1217</v>
       </c>
-      <c r="E68" t="s">
-        <v>1218</v>
-      </c>
       <c r="F68" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G68">
         <v>1701</v>
       </c>
       <c r="H68" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.2">
@@ -13892,19 +14000,19 @@
         <v>67</v>
       </c>
       <c r="D69" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E69" t="s">
         <v>1219</v>
       </c>
-      <c r="E69" t="s">
-        <v>1220</v>
-      </c>
       <c r="F69" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G69">
         <v>1702</v>
       </c>
       <c r="H69" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="70" spans="3:8" x14ac:dyDescent="0.2">
@@ -13912,19 +14020,19 @@
         <v>68</v>
       </c>
       <c r="D70" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E70" t="s">
         <v>1221</v>
       </c>
-      <c r="E70" t="s">
-        <v>1222</v>
-      </c>
       <c r="F70" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G70">
         <v>1703</v>
       </c>
       <c r="H70" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="71" spans="3:8" x14ac:dyDescent="0.2">
@@ -13932,19 +14040,19 @@
         <v>69</v>
       </c>
       <c r="D71" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E71" t="s">
         <v>1223</v>
       </c>
-      <c r="E71" t="s">
-        <v>1224</v>
-      </c>
       <c r="F71" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G71">
         <v>1711</v>
       </c>
       <c r="H71" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="72" spans="3:8" x14ac:dyDescent="0.2">
@@ -13952,19 +14060,19 @@
         <v>70</v>
       </c>
       <c r="D72" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E72" t="s">
         <v>1225</v>
       </c>
-      <c r="E72" t="s">
-        <v>1226</v>
-      </c>
       <c r="F72" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G72">
         <v>1801</v>
       </c>
       <c r="H72" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="73" spans="3:8" x14ac:dyDescent="0.2">
@@ -13972,19 +14080,19 @@
         <v>71</v>
       </c>
       <c r="D73" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E73" t="s">
         <v>1227</v>
       </c>
-      <c r="E73" t="s">
-        <v>1228</v>
-      </c>
       <c r="F73" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G73">
         <v>1811</v>
       </c>
       <c r="H73" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="74" spans="3:8" x14ac:dyDescent="0.2">
@@ -13992,19 +14100,19 @@
         <v>72</v>
       </c>
       <c r="D74" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E74" t="s">
         <v>1229</v>
       </c>
-      <c r="E74" t="s">
-        <v>1230</v>
-      </c>
       <c r="F74" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G74">
         <v>1901</v>
       </c>
       <c r="H74" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="75" spans="3:8" x14ac:dyDescent="0.2">
@@ -14012,19 +14120,19 @@
         <v>73</v>
       </c>
       <c r="D75" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E75" t="s">
         <v>1231</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>1232</v>
-      </c>
-      <c r="F75" t="s">
-        <v>1233</v>
       </c>
       <c r="G75">
         <v>2001</v>
       </c>
       <c r="H75" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="76" spans="3:8" x14ac:dyDescent="0.2">
@@ -14032,19 +14140,19 @@
         <v>74</v>
       </c>
       <c r="D76" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E76" t="s">
         <v>1234</v>
       </c>
-      <c r="E76" t="s">
-        <v>1235</v>
-      </c>
       <c r="F76" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G76">
         <v>2002</v>
       </c>
       <c r="H76" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="77" spans="3:8" x14ac:dyDescent="0.2">
@@ -14052,19 +14160,19 @@
         <v>75</v>
       </c>
       <c r="D77" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E77" t="s">
         <v>1236</v>
       </c>
-      <c r="E77" t="s">
-        <v>1237</v>
-      </c>
       <c r="F77" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G77">
         <v>2003</v>
       </c>
       <c r="H77" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="78" spans="3:8" x14ac:dyDescent="0.2">
@@ -14072,19 +14180,19 @@
         <v>76</v>
       </c>
       <c r="D78" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E78" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="F78" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G78">
         <v>2004</v>
       </c>
       <c r="H78" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="79" spans="3:8" x14ac:dyDescent="0.2">
@@ -14092,19 +14200,19 @@
         <v>77</v>
       </c>
       <c r="D79" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E79" t="s">
         <v>1239</v>
       </c>
-      <c r="E79" t="s">
-        <v>1240</v>
-      </c>
       <c r="F79" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G79">
         <v>2011</v>
       </c>
       <c r="H79" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="80" spans="3:8" x14ac:dyDescent="0.2">
@@ -14112,19 +14220,19 @@
         <v>78</v>
       </c>
       <c r="D80" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E80" t="s">
         <v>1241</v>
       </c>
-      <c r="E80" t="s">
-        <v>1242</v>
-      </c>
       <c r="F80" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G80">
         <v>2012</v>
       </c>
       <c r="H80" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="81" spans="3:8" x14ac:dyDescent="0.2">
@@ -14132,19 +14240,19 @@
         <v>79</v>
       </c>
       <c r="D81" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E81" t="s">
         <v>1243</v>
       </c>
-      <c r="E81" t="s">
-        <v>1244</v>
-      </c>
       <c r="F81" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G81">
         <v>2021</v>
       </c>
       <c r="H81" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="82" spans="3:8" x14ac:dyDescent="0.2">
@@ -14152,19 +14260,19 @@
         <v>80</v>
       </c>
       <c r="D82" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E82" t="s">
         <v>1245</v>
       </c>
-      <c r="E82" t="s">
-        <v>1246</v>
-      </c>
       <c r="F82" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G82">
         <v>2101</v>
       </c>
       <c r="H82" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="83" spans="3:8" x14ac:dyDescent="0.2">
@@ -14172,19 +14280,19 @@
         <v>81</v>
       </c>
       <c r="D83" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E83" t="s">
         <v>1247</v>
       </c>
-      <c r="E83" t="s">
-        <v>1248</v>
-      </c>
       <c r="F83" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G83">
         <v>2111</v>
       </c>
       <c r="H83" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="84" spans="3:8" x14ac:dyDescent="0.2">
@@ -14192,19 +14300,19 @@
         <v>82</v>
       </c>
       <c r="D84" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E84" t="s">
         <v>1249</v>
       </c>
-      <c r="E84" t="s">
-        <v>1250</v>
-      </c>
       <c r="F84" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G84">
         <v>2201</v>
       </c>
       <c r="H84" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="85" spans="3:8" x14ac:dyDescent="0.2">
@@ -14212,19 +14320,19 @@
         <v>83</v>
       </c>
       <c r="D85" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E85" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="F85" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G85">
         <v>2202</v>
       </c>
       <c r="H85" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="86" spans="3:8" x14ac:dyDescent="0.2">
@@ -14232,19 +14340,19 @@
         <v>84</v>
       </c>
       <c r="D86" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E86" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F86" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G86">
         <v>2205</v>
       </c>
       <c r="H86" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="87" spans="3:8" x14ac:dyDescent="0.2">
@@ -14252,19 +14360,19 @@
         <v>85</v>
       </c>
       <c r="D87" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E87" t="s">
         <v>1253</v>
       </c>
-      <c r="E87" t="s">
-        <v>1254</v>
-      </c>
       <c r="F87" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G87">
         <v>2211</v>
       </c>
       <c r="H87" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="88" spans="3:8" x14ac:dyDescent="0.2">
@@ -14272,19 +14380,19 @@
         <v>86</v>
       </c>
       <c r="D88" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E88" t="s">
         <v>1255</v>
       </c>
-      <c r="E88" t="s">
-        <v>1256</v>
-      </c>
       <c r="F88" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G88">
         <v>2221</v>
       </c>
       <c r="H88" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="89" spans="3:8" x14ac:dyDescent="0.2">
@@ -14292,19 +14400,19 @@
         <v>87</v>
       </c>
       <c r="D89" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E89" t="s">
         <v>1257</v>
       </c>
-      <c r="E89" t="s">
-        <v>1258</v>
-      </c>
       <c r="F89" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G89">
         <v>2231</v>
       </c>
       <c r="H89" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="90" spans="3:8" x14ac:dyDescent="0.2">
@@ -14312,19 +14420,19 @@
         <v>88</v>
       </c>
       <c r="D90" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E90" t="s">
         <v>1259</v>
       </c>
-      <c r="E90" t="s">
-        <v>1260</v>
-      </c>
       <c r="F90" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G90">
         <v>2232</v>
       </c>
       <c r="H90" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="91" spans="3:8" x14ac:dyDescent="0.2">
@@ -14332,19 +14440,19 @@
         <v>89</v>
       </c>
       <c r="D91" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E91" t="s">
         <v>1261</v>
       </c>
-      <c r="E91" t="s">
-        <v>1262</v>
-      </c>
       <c r="F91" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G91">
         <v>2241</v>
       </c>
       <c r="H91" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="92" spans="3:8" x14ac:dyDescent="0.2">
@@ -14352,19 +14460,19 @@
         <v>90</v>
       </c>
       <c r="D92" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E92" t="s">
         <v>1263</v>
       </c>
-      <c r="E92" t="s">
-        <v>1264</v>
-      </c>
       <c r="F92" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G92">
         <v>2251</v>
       </c>
       <c r="H92" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="93" spans="3:8" x14ac:dyDescent="0.2">
@@ -14372,19 +14480,19 @@
         <v>91</v>
       </c>
       <c r="D93" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E93" t="s">
         <v>1265</v>
       </c>
-      <c r="E93" t="s">
-        <v>1266</v>
-      </c>
       <c r="F93" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G93">
         <v>2261</v>
       </c>
       <c r="H93" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="94" spans="3:8" x14ac:dyDescent="0.2">
@@ -14392,19 +14500,19 @@
         <v>92</v>
       </c>
       <c r="D94" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E94" t="s">
         <v>1267</v>
       </c>
-      <c r="E94" t="s">
-        <v>1268</v>
-      </c>
       <c r="F94" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G94">
         <v>2311</v>
       </c>
       <c r="H94" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="95" spans="3:8" x14ac:dyDescent="0.2">
@@ -14412,19 +14520,19 @@
         <v>93</v>
       </c>
       <c r="D95" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E95" t="s">
         <v>1269</v>
       </c>
-      <c r="E95" t="s">
-        <v>1270</v>
-      </c>
       <c r="F95" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G95">
         <v>2312</v>
       </c>
       <c r="H95" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="96" spans="3:8" x14ac:dyDescent="0.2">
@@ -14432,19 +14540,19 @@
         <v>94</v>
       </c>
       <c r="D96" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E96" t="s">
         <v>1272</v>
       </c>
-      <c r="E96" t="s">
-        <v>1273</v>
-      </c>
       <c r="F96" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G96">
         <v>2313</v>
       </c>
       <c r="H96" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="97" spans="3:8" x14ac:dyDescent="0.2">
@@ -14452,19 +14560,19 @@
         <v>95</v>
       </c>
       <c r="D97" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E97" t="s">
         <v>1274</v>
       </c>
-      <c r="E97" t="s">
-        <v>1275</v>
-      </c>
       <c r="F97" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G97">
         <v>2314</v>
       </c>
       <c r="H97" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="98" spans="3:8" x14ac:dyDescent="0.2">
@@ -14472,19 +14580,19 @@
         <v>96</v>
       </c>
       <c r="D98" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E98" t="s">
         <v>1276</v>
       </c>
-      <c r="E98" t="s">
-        <v>1277</v>
-      </c>
       <c r="F98" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G98">
         <v>2401</v>
       </c>
       <c r="H98" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="99" spans="3:8" x14ac:dyDescent="0.2">
@@ -14492,19 +14600,19 @@
         <v>97</v>
       </c>
       <c r="D99" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E99" t="s">
         <v>1278</v>
       </c>
-      <c r="E99" t="s">
-        <v>1279</v>
-      </c>
       <c r="F99" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G99">
         <v>2411</v>
       </c>
       <c r="H99" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="100" spans="3:8" x14ac:dyDescent="0.2">
@@ -14512,19 +14620,19 @@
         <v>98</v>
       </c>
       <c r="D100" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E100" t="s">
         <v>1280</v>
       </c>
-      <c r="E100" t="s">
-        <v>1281</v>
-      </c>
       <c r="F100" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G100">
         <v>2501</v>
       </c>
       <c r="H100" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="101" spans="3:8" x14ac:dyDescent="0.2">
@@ -14532,19 +14640,19 @@
         <v>99</v>
       </c>
       <c r="D101" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E101" t="s">
         <v>1282</v>
       </c>
-      <c r="E101" t="s">
-        <v>1283</v>
-      </c>
       <c r="F101" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G101">
         <v>2601</v>
       </c>
       <c r="H101" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="102" spans="3:8" x14ac:dyDescent="0.2">
@@ -14552,19 +14660,19 @@
         <v>100</v>
       </c>
       <c r="D102" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E102" t="s">
         <v>1284</v>
       </c>
-      <c r="E102" t="s">
-        <v>1285</v>
-      </c>
       <c r="F102" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G102">
         <v>2602</v>
       </c>
       <c r="H102" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="103" spans="3:8" x14ac:dyDescent="0.2">
@@ -14572,19 +14680,19 @@
         <v>101</v>
       </c>
       <c r="D103" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E103" t="s">
         <v>1286</v>
       </c>
-      <c r="E103" t="s">
-        <v>1287</v>
-      </c>
       <c r="F103" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G103">
         <v>2701</v>
       </c>
       <c r="H103" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="104" spans="3:8" x14ac:dyDescent="0.2">
@@ -14592,19 +14700,19 @@
         <v>102</v>
       </c>
       <c r="D104" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E104" t="s">
         <v>1288</v>
       </c>
-      <c r="E104" t="s">
-        <v>1289</v>
-      </c>
       <c r="F104" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G104">
         <v>2702</v>
       </c>
       <c r="H104" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="105" spans="3:8" x14ac:dyDescent="0.2">
@@ -14612,19 +14720,19 @@
         <v>103</v>
       </c>
       <c r="D105" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E105" t="s">
         <v>1290</v>
       </c>
-      <c r="E105" t="s">
-        <v>1291</v>
-      </c>
       <c r="F105" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G105">
         <v>2711</v>
       </c>
       <c r="H105" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="106" spans="3:8" x14ac:dyDescent="0.2">
@@ -14632,19 +14740,19 @@
         <v>104</v>
       </c>
       <c r="D106" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E106" t="s">
         <v>1292</v>
       </c>
-      <c r="E106" t="s">
-        <v>1293</v>
-      </c>
       <c r="F106" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G106">
         <v>2721</v>
       </c>
       <c r="H106" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="107" spans="3:8" x14ac:dyDescent="0.2">
@@ -14652,19 +14760,19 @@
         <v>105</v>
       </c>
       <c r="D107" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E107" t="s">
         <v>1294</v>
       </c>
-      <c r="E107" t="s">
-        <v>1295</v>
-      </c>
       <c r="F107" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G107">
         <v>2801</v>
       </c>
       <c r="H107" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="108" spans="3:8" x14ac:dyDescent="0.2">
@@ -14672,19 +14780,19 @@
         <v>106</v>
       </c>
       <c r="D108" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E108" t="s">
         <v>1296</v>
       </c>
-      <c r="E108" t="s">
-        <v>1297</v>
-      </c>
       <c r="F108" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G108">
         <v>2802</v>
       </c>
       <c r="H108" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="109" spans="3:8" x14ac:dyDescent="0.2">
@@ -14692,19 +14800,19 @@
         <v>107</v>
       </c>
       <c r="D109" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E109" t="s">
         <v>1298</v>
       </c>
-      <c r="E109" t="s">
-        <v>1299</v>
-      </c>
       <c r="F109" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G109">
         <v>2811</v>
       </c>
       <c r="H109" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="110" spans="3:8" x14ac:dyDescent="0.2">
@@ -14712,19 +14820,19 @@
         <v>108</v>
       </c>
       <c r="D110" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E110" t="s">
         <v>1300</v>
       </c>
-      <c r="E110" t="s">
-        <v>1301</v>
-      </c>
       <c r="F110" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G110">
         <v>2901</v>
       </c>
       <c r="H110" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="111" spans="3:8" x14ac:dyDescent="0.2">
@@ -14732,19 +14840,19 @@
         <v>109</v>
       </c>
       <c r="D111" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E111" t="s">
         <v>1302</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>1303</v>
-      </c>
-      <c r="F111" t="s">
-        <v>1304</v>
       </c>
       <c r="G111">
         <v>3001</v>
       </c>
       <c r="H111" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="112" spans="3:8" x14ac:dyDescent="0.2">
@@ -14752,19 +14860,19 @@
         <v>110</v>
       </c>
       <c r="D112" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E112" t="s">
         <v>1305</v>
       </c>
-      <c r="E112" t="s">
-        <v>1306</v>
-      </c>
       <c r="F112" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G112">
         <v>3002</v>
       </c>
       <c r="H112" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="113" spans="3:8" x14ac:dyDescent="0.2">
@@ -14772,19 +14880,19 @@
         <v>111</v>
       </c>
       <c r="D113" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E113" t="s">
         <v>1307</v>
       </c>
-      <c r="E113" t="s">
-        <v>1308</v>
-      </c>
       <c r="F113" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G113">
         <v>3101</v>
       </c>
       <c r="H113" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="114" spans="3:8" x14ac:dyDescent="0.2">
@@ -14792,19 +14900,19 @@
         <v>112</v>
       </c>
       <c r="D114" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E114" t="s">
         <v>1309</v>
       </c>
-      <c r="E114" t="s">
-        <v>1310</v>
-      </c>
       <c r="F114" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G114">
         <v>3201</v>
       </c>
       <c r="H114" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="115" spans="3:8" x14ac:dyDescent="0.2">
@@ -14812,19 +14920,19 @@
         <v>113</v>
       </c>
       <c r="D115" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E115" t="s">
         <v>1311</v>
       </c>
-      <c r="E115" t="s">
-        <v>1312</v>
-      </c>
       <c r="F115" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G115">
         <v>3202</v>
       </c>
       <c r="H115" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="116" spans="3:8" x14ac:dyDescent="0.2">
@@ -14832,19 +14940,19 @@
         <v>114</v>
       </c>
       <c r="D116" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E116" t="s">
         <v>1313</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>1314</v>
-      </c>
-      <c r="F116" t="s">
-        <v>1315</v>
       </c>
       <c r="G116">
         <v>4001</v>
       </c>
       <c r="H116" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="117" spans="3:8" x14ac:dyDescent="0.2">
@@ -14852,19 +14960,19 @@
         <v>115</v>
       </c>
       <c r="D117" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E117" t="s">
         <v>1316</v>
       </c>
-      <c r="E117" t="s">
-        <v>1317</v>
-      </c>
       <c r="F117" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G117">
         <v>4002</v>
       </c>
       <c r="H117" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="118" spans="3:8" x14ac:dyDescent="0.2">
@@ -14872,19 +14980,19 @@
         <v>116</v>
       </c>
       <c r="D118" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E118" t="s">
         <v>1318</v>
       </c>
-      <c r="E118" t="s">
-        <v>1319</v>
-      </c>
       <c r="F118" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G118">
         <v>4101</v>
       </c>
       <c r="H118" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="119" spans="3:8" x14ac:dyDescent="0.2">
@@ -14892,19 +15000,19 @@
         <v>117</v>
       </c>
       <c r="D119" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E119" t="s">
         <v>1320</v>
       </c>
-      <c r="E119" t="s">
-        <v>1321</v>
-      </c>
       <c r="F119" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G119">
         <v>4102</v>
       </c>
       <c r="H119" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="120" spans="3:8" x14ac:dyDescent="0.2">
@@ -14912,19 +15020,19 @@
         <v>118</v>
       </c>
       <c r="D120" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E120" t="s">
         <v>1322</v>
       </c>
-      <c r="E120" t="s">
-        <v>1323</v>
-      </c>
       <c r="F120" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G120">
         <v>4103</v>
       </c>
       <c r="H120" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="121" spans="3:8" x14ac:dyDescent="0.2">
@@ -14932,19 +15040,19 @@
         <v>119</v>
       </c>
       <c r="D121" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E121" t="s">
         <v>1324</v>
       </c>
-      <c r="E121" t="s">
-        <v>1325</v>
-      </c>
       <c r="F121" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G121">
         <v>4104</v>
       </c>
       <c r="H121" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="122" spans="3:8" x14ac:dyDescent="0.2">
@@ -14952,19 +15060,19 @@
         <v>120</v>
       </c>
       <c r="D122" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E122" t="s">
         <v>1326</v>
       </c>
-      <c r="E122" t="s">
-        <v>1327</v>
-      </c>
       <c r="F122" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G122">
         <v>4201</v>
       </c>
       <c r="H122" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="123" spans="3:8" x14ac:dyDescent="0.2">
@@ -14972,19 +15080,19 @@
         <v>121</v>
       </c>
       <c r="D123" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E123" t="s">
         <v>1328</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>1329</v>
-      </c>
-      <c r="F123" t="s">
-        <v>1330</v>
       </c>
       <c r="G123">
         <v>5001</v>
       </c>
       <c r="H123" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="124" spans="3:8" x14ac:dyDescent="0.2">
@@ -14992,19 +15100,19 @@
         <v>122</v>
       </c>
       <c r="D124" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E124" t="s">
         <v>1331</v>
       </c>
-      <c r="E124" t="s">
-        <v>1332</v>
-      </c>
       <c r="F124" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G124">
         <v>5101</v>
       </c>
       <c r="H124" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="125" spans="3:8" x14ac:dyDescent="0.2">
@@ -15012,19 +15120,19 @@
         <v>123</v>
       </c>
       <c r="D125" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E125" t="s">
         <v>1333</v>
       </c>
-      <c r="E125" t="s">
-        <v>1334</v>
-      </c>
       <c r="F125" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G125">
         <v>5201</v>
       </c>
       <c r="H125" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="126" spans="3:8" x14ac:dyDescent="0.2">
@@ -15032,19 +15140,19 @@
         <v>124</v>
       </c>
       <c r="D126" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E126" t="s">
         <v>1335</v>
       </c>
-      <c r="E126" t="s">
-        <v>1336</v>
-      </c>
       <c r="F126" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G126">
         <v>5301</v>
       </c>
       <c r="H126" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="127" spans="3:8" x14ac:dyDescent="0.2">
@@ -15052,19 +15160,19 @@
         <v>125</v>
       </c>
       <c r="D127" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E127" t="s">
         <v>1337</v>
       </c>
-      <c r="E127" t="s">
-        <v>1338</v>
-      </c>
       <c r="F127" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G127">
         <v>5401</v>
       </c>
       <c r="H127" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="128" spans="3:8" x14ac:dyDescent="0.2">
@@ -15072,19 +15180,19 @@
         <v>126</v>
       </c>
       <c r="D128" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E128" t="s">
         <v>1339</v>
       </c>
-      <c r="E128" t="s">
-        <v>1340</v>
-      </c>
       <c r="F128" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G128">
         <v>5402</v>
       </c>
       <c r="H128" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="129" spans="3:8" x14ac:dyDescent="0.2">
@@ -15092,19 +15200,19 @@
         <v>127</v>
       </c>
       <c r="D129" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E129" t="s">
         <v>1341</v>
       </c>
-      <c r="E129" t="s">
-        <v>1342</v>
-      </c>
       <c r="F129" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G129">
         <v>5403</v>
       </c>
       <c r="H129" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="130" spans="3:8" x14ac:dyDescent="0.2">
@@ -15112,19 +15220,19 @@
         <v>128</v>
       </c>
       <c r="D130" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E130" t="s">
         <v>1343</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>1344</v>
-      </c>
-      <c r="F130" t="s">
-        <v>1345</v>
       </c>
       <c r="G130">
         <v>6001</v>
       </c>
       <c r="H130" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="131" spans="3:8" x14ac:dyDescent="0.2">
@@ -15132,19 +15240,19 @@
         <v>129</v>
       </c>
       <c r="D131" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E131" t="s">
         <v>1346</v>
       </c>
-      <c r="E131" t="s">
-        <v>1347</v>
-      </c>
       <c r="F131" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G131">
         <v>6011</v>
       </c>
       <c r="H131" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="132" spans="3:8" x14ac:dyDescent="0.2">
@@ -15152,19 +15260,19 @@
         <v>130</v>
       </c>
       <c r="D132" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E132" t="s">
         <v>1348</v>
       </c>
-      <c r="E132" t="s">
-        <v>1349</v>
-      </c>
       <c r="F132" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G132">
         <v>6021</v>
       </c>
       <c r="H132" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="133" spans="3:8" x14ac:dyDescent="0.2">
@@ -15172,19 +15280,19 @@
         <v>131</v>
       </c>
       <c r="D133" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E133" t="s">
         <v>1350</v>
       </c>
-      <c r="E133" t="s">
-        <v>1351</v>
-      </c>
       <c r="F133" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G133">
         <v>6031</v>
       </c>
       <c r="H133" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="134" spans="3:8" x14ac:dyDescent="0.2">
@@ -15192,19 +15300,19 @@
         <v>132</v>
       </c>
       <c r="D134" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E134" t="s">
         <v>1352</v>
       </c>
-      <c r="E134" t="s">
-        <v>1353</v>
-      </c>
       <c r="F134" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G134">
         <v>6032</v>
       </c>
       <c r="H134" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="135" spans="3:8" x14ac:dyDescent="0.2">
@@ -15212,19 +15320,19 @@
         <v>133</v>
       </c>
       <c r="D135" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E135" t="s">
         <v>1354</v>
       </c>
-      <c r="E135" t="s">
-        <v>1355</v>
-      </c>
       <c r="F135" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G135">
         <v>6041</v>
       </c>
       <c r="H135" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="136" spans="3:8" x14ac:dyDescent="0.2">
@@ -15232,19 +15340,19 @@
         <v>134</v>
       </c>
       <c r="D136" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E136" t="s">
         <v>1356</v>
       </c>
-      <c r="E136" t="s">
-        <v>1357</v>
-      </c>
       <c r="F136" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G136">
         <v>6051</v>
       </c>
       <c r="H136" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="137" spans="3:8" x14ac:dyDescent="0.2">
@@ -15252,19 +15360,19 @@
         <v>135</v>
       </c>
       <c r="D137" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E137" t="s">
         <v>1358</v>
       </c>
-      <c r="E137" t="s">
-        <v>1359</v>
-      </c>
       <c r="F137" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G137">
         <v>6061</v>
       </c>
       <c r="H137" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="138" spans="3:8" x14ac:dyDescent="0.2">
@@ -15272,19 +15380,19 @@
         <v>136</v>
       </c>
       <c r="D138" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E138" t="s">
         <v>1361</v>
       </c>
-      <c r="E138" t="s">
-        <v>1362</v>
-      </c>
       <c r="F138" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G138">
         <v>6101</v>
       </c>
       <c r="H138" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="139" spans="3:8" x14ac:dyDescent="0.2">
@@ -15292,19 +15400,19 @@
         <v>137</v>
       </c>
       <c r="D139" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E139" t="s">
         <v>1363</v>
       </c>
-      <c r="E139" t="s">
-        <v>1364</v>
-      </c>
       <c r="F139" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G139">
         <v>6111</v>
       </c>
       <c r="H139" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="140" spans="3:8" x14ac:dyDescent="0.2">
@@ -15312,19 +15420,19 @@
         <v>138</v>
       </c>
       <c r="D140" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E140" t="s">
         <v>1365</v>
       </c>
-      <c r="E140" t="s">
-        <v>1366</v>
-      </c>
       <c r="F140" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G140">
         <v>6201</v>
       </c>
       <c r="H140" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="141" spans="3:8" x14ac:dyDescent="0.2">
@@ -15332,19 +15440,19 @@
         <v>139</v>
       </c>
       <c r="D141" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E141" t="s">
         <v>1367</v>
       </c>
-      <c r="E141" t="s">
-        <v>1368</v>
-      </c>
       <c r="F141" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G141">
         <v>6202</v>
       </c>
       <c r="H141" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="142" spans="3:8" x14ac:dyDescent="0.2">
@@ -15352,19 +15460,19 @@
         <v>140</v>
       </c>
       <c r="D142" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E142" t="s">
         <v>1369</v>
       </c>
-      <c r="E142" t="s">
-        <v>1370</v>
-      </c>
       <c r="F142" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G142">
         <v>6203</v>
       </c>
       <c r="H142" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="143" spans="3:8" x14ac:dyDescent="0.2">
@@ -15372,19 +15480,19 @@
         <v>141</v>
       </c>
       <c r="D143" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E143" t="s">
         <v>1371</v>
       </c>
-      <c r="E143" t="s">
-        <v>1372</v>
-      </c>
       <c r="F143" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G143">
         <v>6301</v>
       </c>
       <c r="H143" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="144" spans="3:8" x14ac:dyDescent="0.2">
@@ -15392,19 +15500,19 @@
         <v>142</v>
       </c>
       <c r="D144" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E144" t="s">
         <v>1373</v>
       </c>
-      <c r="E144" t="s">
-        <v>1374</v>
-      </c>
       <c r="F144" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G144">
         <v>6401</v>
       </c>
       <c r="H144" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="145" spans="3:8" x14ac:dyDescent="0.2">
@@ -15412,19 +15520,19 @@
         <v>143</v>
       </c>
       <c r="D145" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E145" t="s">
         <v>1375</v>
       </c>
-      <c r="E145" t="s">
-        <v>1376</v>
-      </c>
       <c r="F145" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G145">
         <v>6402</v>
       </c>
       <c r="H145" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="146" spans="3:8" x14ac:dyDescent="0.2">
@@ -15432,19 +15540,19 @@
         <v>144</v>
       </c>
       <c r="D146" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E146" t="s">
         <v>1377</v>
       </c>
-      <c r="E146" t="s">
-        <v>1378</v>
-      </c>
       <c r="F146" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G146">
         <v>6405</v>
       </c>
       <c r="H146" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="147" spans="3:8" x14ac:dyDescent="0.2">
@@ -15452,19 +15560,19 @@
         <v>145</v>
       </c>
       <c r="D147" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E147" t="s">
         <v>1379</v>
       </c>
-      <c r="E147" t="s">
-        <v>1380</v>
-      </c>
       <c r="F147" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G147">
         <v>6411</v>
       </c>
       <c r="H147" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="148" spans="3:8" x14ac:dyDescent="0.2">
@@ -15472,19 +15580,19 @@
         <v>146</v>
       </c>
       <c r="D148" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E148" t="s">
         <v>1381</v>
       </c>
-      <c r="E148" t="s">
-        <v>1382</v>
-      </c>
       <c r="F148" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G148">
         <v>6421</v>
       </c>
       <c r="H148" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="149" spans="3:8" x14ac:dyDescent="0.2">
@@ -15492,19 +15600,19 @@
         <v>147</v>
       </c>
       <c r="D149" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E149" t="s">
         <v>1383</v>
       </c>
-      <c r="E149" t="s">
-        <v>1384</v>
-      </c>
       <c r="F149" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G149">
         <v>6501</v>
       </c>
       <c r="H149" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="150" spans="3:8" x14ac:dyDescent="0.2">
@@ -15512,19 +15620,19 @@
         <v>148</v>
       </c>
       <c r="D150" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E150" t="s">
         <v>1385</v>
       </c>
-      <c r="E150" t="s">
-        <v>1386</v>
-      </c>
       <c r="F150" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G150">
         <v>6502</v>
       </c>
       <c r="H150" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="151" spans="3:8" x14ac:dyDescent="0.2">
@@ -15532,19 +15640,19 @@
         <v>149</v>
       </c>
       <c r="D151" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E151" t="s">
         <v>1387</v>
       </c>
-      <c r="E151" t="s">
-        <v>1388</v>
-      </c>
       <c r="F151" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G151">
         <v>6511</v>
       </c>
       <c r="H151" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="152" spans="3:8" x14ac:dyDescent="0.2">
@@ -15552,19 +15660,19 @@
         <v>150</v>
       </c>
       <c r="D152" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E152" t="s">
         <v>1389</v>
       </c>
-      <c r="E152" t="s">
-        <v>1390</v>
-      </c>
       <c r="F152" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G152">
         <v>6521</v>
       </c>
       <c r="H152" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="153" spans="3:8" x14ac:dyDescent="0.2">
@@ -15572,19 +15680,19 @@
         <v>151</v>
       </c>
       <c r="D153" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E153" t="s">
         <v>1391</v>
       </c>
-      <c r="E153" t="s">
-        <v>1392</v>
-      </c>
       <c r="F153" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G153">
         <v>6531</v>
       </c>
       <c r="H153" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="154" spans="3:8" x14ac:dyDescent="0.2">
@@ -15592,19 +15700,19 @@
         <v>152</v>
       </c>
       <c r="D154" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E154" t="s">
         <v>1393</v>
       </c>
-      <c r="E154" t="s">
-        <v>1394</v>
-      </c>
       <c r="F154" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G154">
         <v>6541</v>
       </c>
       <c r="H154" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="155" spans="3:8" x14ac:dyDescent="0.2">
@@ -15612,19 +15720,19 @@
         <v>153</v>
       </c>
       <c r="D155" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E155" t="s">
         <v>1395</v>
       </c>
-      <c r="E155" t="s">
-        <v>1396</v>
-      </c>
       <c r="F155" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G155">
         <v>6542</v>
       </c>
       <c r="H155" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="156" spans="3:8" x14ac:dyDescent="0.2">
@@ -15632,19 +15740,19 @@
         <v>154</v>
       </c>
       <c r="D156" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E156" t="s">
         <v>1397</v>
       </c>
-      <c r="E156" t="s">
-        <v>1398</v>
-      </c>
       <c r="F156" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G156">
         <v>6601</v>
       </c>
       <c r="H156" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="157" spans="3:8" x14ac:dyDescent="0.2">
@@ -15652,19 +15760,19 @@
         <v>155</v>
       </c>
       <c r="D157" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E157" t="s">
         <v>1399</v>
       </c>
-      <c r="E157" t="s">
-        <v>1400</v>
-      </c>
       <c r="F157" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G157">
         <v>6602</v>
       </c>
       <c r="H157" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="158" spans="3:8" x14ac:dyDescent="0.2">
@@ -15672,19 +15780,19 @@
         <v>156</v>
       </c>
       <c r="D158" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E158" t="s">
         <v>1401</v>
       </c>
-      <c r="E158" t="s">
-        <v>1402</v>
-      </c>
       <c r="F158" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G158">
         <v>6603</v>
       </c>
       <c r="H158" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="159" spans="3:8" x14ac:dyDescent="0.2">
@@ -15692,19 +15800,19 @@
         <v>157</v>
       </c>
       <c r="D159" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E159" t="s">
         <v>1403</v>
       </c>
-      <c r="E159" t="s">
-        <v>1404</v>
-      </c>
       <c r="F159" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G159">
         <v>6604</v>
       </c>
       <c r="H159" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="160" spans="3:8" x14ac:dyDescent="0.2">
@@ -15712,19 +15820,19 @@
         <v>158</v>
       </c>
       <c r="D160" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E160" t="s">
         <v>1405</v>
       </c>
-      <c r="E160" t="s">
-        <v>1406</v>
-      </c>
       <c r="F160" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G160">
         <v>6701</v>
       </c>
       <c r="H160" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="161" spans="3:8" x14ac:dyDescent="0.2">
@@ -15732,19 +15840,19 @@
         <v>159</v>
       </c>
       <c r="D161" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E161" t="s">
         <v>1407</v>
       </c>
-      <c r="E161" t="s">
-        <v>1408</v>
-      </c>
       <c r="F161" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G161">
         <v>6711</v>
       </c>
       <c r="H161" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="162" spans="3:8" x14ac:dyDescent="0.2">
@@ -15752,19 +15860,19 @@
         <v>160</v>
       </c>
       <c r="D162" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E162" t="s">
         <v>1409</v>
       </c>
-      <c r="E162" t="s">
-        <v>1410</v>
-      </c>
       <c r="F162" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G162">
         <v>6801</v>
       </c>
       <c r="H162" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="163" spans="3:8" x14ac:dyDescent="0.2">
@@ -15772,19 +15880,19 @@
         <v>161</v>
       </c>
       <c r="D163" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E163" t="s">
         <v>1411</v>
       </c>
-      <c r="E163" t="s">
-        <v>1412</v>
-      </c>
       <c r="F163" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G163">
         <v>6901</v>
       </c>
       <c r="H163" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
   </sheetData>
@@ -15811,22 +15919,22 @@
         <v>998</v>
       </c>
       <c r="D2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="E2" t="s">
         <v>1004</v>
       </c>
       <c r="F2" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="G2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="I2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="3" spans="3:9" x14ac:dyDescent="0.2">
@@ -15837,7 +15945,7 @@
         <v>1002</v>
       </c>
       <c r="E3" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F3">
         <v>200000</v>
@@ -15860,7 +15968,7 @@
         <v>4001</v>
       </c>
       <c r="E4" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F4">
         <v>100000</v>
@@ -15883,7 +15991,7 @@
         <v>4001</v>
       </c>
       <c r="E5" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F5">
         <v>60000</v>
@@ -15906,7 +16014,7 @@
         <v>4001</v>
       </c>
       <c r="E6" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="F6">
         <v>40000</v>
@@ -15946,19 +16054,19 @@
         <v>998</v>
       </c>
       <c r="D2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E2" t="s">
         <v>1004</v>
       </c>
       <c r="F2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="G2" t="s">
         <v>1037</v>
       </c>
       <c r="H2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.2">
@@ -15969,16 +16077,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="F3" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="G3" s="2">
         <v>45129.574999999997</v>
       </c>
       <c r="H3" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
   </sheetData>
@@ -16016,7 +16124,7 @@
         <v>1037</v>
       </c>
       <c r="G2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
@@ -16024,10 +16132,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -16036,7 +16144,7 @@
         <v>45129.574999999997</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBADF8A-2D53-467B-917A-52828826A353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D90004-D894-4E01-8C06-B1D2D68B5639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10377,7 +10377,7 @@
     </row>
     <row r="469" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B469">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C469" t="s">
         <v>930</v>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>39376.176381075384</v>
+        <v>44282.271285203329</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>37446.542880537068</v>
+        <v>42942.100478939465</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36411.541339806747</v>
+        <v>41725.979007820781</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37021.343457043185</v>
+        <v>35826.104824848553</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41862.780972037763</v>
+        <v>37848.502173441608</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41141.331984896715</v>
+        <v>37005.895688841578</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40737.584973109711</v>
+        <v>39487.401066377985</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36663.822738185001</v>
+        <v>38728.897511006267</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36054.873660656966</v>
+        <v>39162.416261824677</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40677.37141947019</v>
+        <v>40221.992551946038</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42570.500409609078</v>
+        <v>42375.636766531818</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44579.374396718056</v>
+        <v>42608.42394536436</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12193,7 +12193,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42930.657935193303</v>
+        <v>35777.506828477337</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43225.462032391471</v>
+        <v>38159.370520529294</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43771.078392757445</v>
+        <v>41256.465402303795</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44624.689090226995</v>
+        <v>39765.033154840945</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44272.827548197449</v>
+        <v>42784.329021174715</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39874.041318655887</v>
+        <v>38882.139790791771</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38644.721966224562</v>
+        <v>42634.66828529552</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37349.220562157818</v>
+        <v>35894.998563080488</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12393,7 +12393,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41892.460311830037</v>
+        <v>42317.427498144891</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36414.469033721878</v>
+        <v>43589.121107539409</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41755.736868250904</v>
+        <v>39034.44487155461</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43691.602923708924</v>
+        <v>38870.312691644307</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38111.033206565167</v>
+        <v>40025.602001150968</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44441.420961858552</v>
+        <v>36034.216733445792</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38582.446778760786</v>
+        <v>41341.2431685595</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36952.703192369343</v>
+        <v>38966.390159304625</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39033.0432240265</v>
+        <v>40109.118347641866</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37366.423738125617</v>
+        <v>35605.141649111829</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -16143,8 +16143,8 @@
       <c r="F3" s="2">
         <v>45129.574999999997</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>1416</v>
+      <c r="G3" s="3" t="s">
+        <v>1426</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D90004-D894-4E01-8C06-B1D2D68B5639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21BC53D-678E-4025-83FF-CDE3AB3B08F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_company" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="1475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="1476">
   <si>
     <t>Walmart</t>
   </si>
@@ -4705,10 +4705,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>银行存款-天月桥支行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>实收资本-林正东</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4733,10 +4729,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>收股东投资款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>WMT账套01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4749,10 +4741,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>objects</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4892,6 +4880,21 @@
   </si>
   <si>
     <t>{"url": "C:/Users/Administrator/Pictures/fumarate/sale.jpg", "price": 5.927287739472007, "price_striked": 5.111}</t>
+  </si>
+  <si>
+    <t>收到股东弗拉克-J-法博齐的投资款</t>
+  </si>
+  <si>
+    <t>收到股东弗拉克-J-法博齐的投资款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["资本"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行存款-招商银行股份有限公司上海天钥桥支行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -10796,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="D2" t="s">
         <v>1003</v>
@@ -10976,7 +10979,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="D11" t="s">
         <v>1034</v>
@@ -11052,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="F2" s="2">
         <v>45072.29583333333</v>
@@ -11072,7 +11075,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="F3" s="2">
         <v>45072.29583333333</v>
@@ -11092,7 +11095,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="F4" s="2">
         <v>45072.29583333333</v>
@@ -11112,7 +11115,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="F5" s="2">
         <v>45072.29583333333</v>
@@ -11132,7 +11135,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="F6" s="2">
         <v>45072.29583333333</v>
@@ -11152,7 +11155,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="F7" s="2">
         <v>45072.29583333333</v>
@@ -11172,7 +11175,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="F8" s="2">
         <v>45072.29583333333</v>
@@ -11192,7 +11195,7 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="F9" s="2">
         <v>45072.29583333333</v>
@@ -11212,7 +11215,7 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="F10" s="2">
         <v>45072.29583333333</v>
@@ -11232,7 +11235,7 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="F11" s="2">
         <v>45072.29583333333</v>
@@ -11252,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="F12" s="2">
         <v>45072.29583333333</v>
@@ -11272,7 +11275,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="F13" s="2">
         <v>45072.29583333333</v>
@@ -11292,7 +11295,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="F14" s="2">
         <v>45072.29583333333</v>
@@ -11312,7 +11315,7 @@
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="F15" s="2">
         <v>45072.29583333333</v>
@@ -11332,7 +11335,7 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="F16" s="2">
         <v>45072.29583333333</v>
@@ -11352,7 +11355,7 @@
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="F17" s="2">
         <v>45072.29583333333</v>
@@ -11372,7 +11375,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="F18" s="2">
         <v>45072.29583333333</v>
@@ -11392,7 +11395,7 @@
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="F19" s="2">
         <v>45072.29583333333</v>
@@ -11412,7 +11415,7 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="F20" s="2">
         <v>45072.29583333333</v>
@@ -11432,7 +11435,7 @@
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="F21" s="2">
         <v>45072.29583333333</v>
@@ -11452,7 +11455,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="F22" s="2">
         <v>45072.29583333333</v>
@@ -11472,7 +11475,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="F23" s="2">
         <v>45072.29583333333</v>
@@ -11492,7 +11495,7 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="F24" s="2">
         <v>45072.29583333333</v>
@@ -11512,7 +11515,7 @@
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="F25" s="2">
         <v>45072.29583333333</v>
@@ -11532,7 +11535,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="F26" s="2">
         <v>45072.29583333333</v>
@@ -11552,7 +11555,7 @@
         <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="F27" s="2">
         <v>45072.29583333333</v>
@@ -11572,7 +11575,7 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="F28" s="2">
         <v>45072.29583333333</v>
@@ -11592,7 +11595,7 @@
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="F29" s="2">
         <v>45072.29583333333</v>
@@ -11612,7 +11615,7 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="F30" s="2">
         <v>45072.29583333333</v>
@@ -11632,7 +11635,7 @@
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="F31" s="2">
         <v>45072.29583333333</v>
@@ -11652,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="F32" s="2">
         <v>45072.29583333333</v>
@@ -11672,7 +11675,7 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="F33" s="2">
         <v>45072.29583333333</v>
@@ -11692,7 +11695,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="F34" s="2">
         <v>45072.29583333333</v>
@@ -11712,7 +11715,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="F35" s="2">
         <v>45072.29583333333</v>
@@ -11732,7 +11735,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="F36" s="2">
         <v>45072.29583333333</v>
@@ -11752,7 +11755,7 @@
         <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="F37" s="2">
         <v>45072.29583333333</v>
@@ -11772,7 +11775,7 @@
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="F38" s="2">
         <v>45072.29583333333</v>
@@ -11792,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="E39" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="F39" s="2">
         <v>45072.29583333333</v>
@@ -11812,7 +11815,7 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="F40" s="2">
         <v>45072.29583333333</v>
@@ -11832,7 +11835,7 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="F41" s="2">
         <v>45072.29583333333</v>
@@ -11893,7 +11896,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>44282.271285203329</v>
+        <v>42925.320903603984</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11918,7 +11921,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>42942.100478939465</v>
+        <v>44646.255238394704</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -11943,7 +11946,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41725.979007820781</v>
+        <v>44616.624831157416</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -11968,7 +11971,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35826.104824848553</v>
+        <v>41011.821786769127</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -11993,7 +11996,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37848.502173441608</v>
+        <v>38098.65390932891</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -12018,7 +12021,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37005.895688841578</v>
+        <v>36193.347921871347</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -12043,7 +12046,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39487.401066377985</v>
+        <v>44257.007126525838</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -12068,7 +12071,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38728.897511006267</v>
+        <v>36976.719584099759</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -12093,7 +12096,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39162.416261824677</v>
+        <v>39921.452193659759</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12118,7 +12121,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40221.992551946038</v>
+        <v>40830.770036896254</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12143,7 +12146,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42375.636766531818</v>
+        <v>38374.263447951082</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12168,7 +12171,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42608.42394536436</v>
+        <v>37466.687638836469</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12193,7 +12196,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35777.506828477337</v>
+        <v>40912.384989805549</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12218,7 +12221,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38159.370520529294</v>
+        <v>40154.501371960832</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12243,7 +12246,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41256.465402303795</v>
+        <v>43678.9634574515</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12268,7 +12271,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39765.033154840945</v>
+        <v>38181.783900576556</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12293,7 +12296,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42784.329021174715</v>
+        <v>43246.25346372513</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12318,7 +12321,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38882.139790791771</v>
+        <v>43357.3929326488</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12343,7 +12346,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42634.66828529552</v>
+        <v>38100.606110066641</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12368,7 +12371,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35894.998563080488</v>
+        <v>36250.83898379976</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12393,7 +12396,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42317.427498144891</v>
+        <v>36613.916401759197</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12418,7 +12421,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43589.121107539409</v>
+        <v>40784.077867813729</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12443,7 +12446,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39034.44487155461</v>
+        <v>37025.142982572172</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12468,7 +12471,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38870.312691644307</v>
+        <v>41282.583133026572</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12493,7 +12496,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40025.602001150968</v>
+        <v>38309.801706100443</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12518,7 +12521,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36034.216733445792</v>
+        <v>41529.013966300983</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12543,7 +12546,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41341.2431685595</v>
+        <v>38834.097447179658</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12568,7 +12571,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38966.390159304625</v>
+        <v>35338.158722646665</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12593,7 +12596,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40109.118347641866</v>
+        <v>40574.01362182117</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12618,7 +12621,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35605.141649111829</v>
+        <v>36675.826620002881</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -12660,16 +12663,16 @@
         <v>998</v>
       </c>
       <c r="D2" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="E2" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="F2" t="s">
         <v>1077</v>
       </c>
       <c r="G2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2" t="s">
         <v>1078</v>
@@ -15908,7 +15911,7 @@
   <cols>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
@@ -15919,7 +15922,7 @@
         <v>998</v>
       </c>
       <c r="D2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="E2" t="s">
         <v>1004</v>
@@ -15928,13 +15931,13 @@
         <v>1417</v>
       </c>
       <c r="G2" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="H2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="I2" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="3" spans="3:9" x14ac:dyDescent="0.2">
@@ -15945,7 +15948,7 @@
         <v>1002</v>
       </c>
       <c r="E3" t="s">
-        <v>1418</v>
+        <v>1475</v>
       </c>
       <c r="F3">
         <v>200000</v>
@@ -15968,7 +15971,7 @@
         <v>4001</v>
       </c>
       <c r="E4" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="F4">
         <v>100000</v>
@@ -15991,7 +15994,7 @@
         <v>4001</v>
       </c>
       <c r="E5" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F5">
         <v>60000</v>
@@ -16014,7 +16017,7 @@
         <v>4001</v>
       </c>
       <c r="E6" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F6">
         <v>40000</v>
@@ -16043,10 +16046,10 @@
   <cols>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:8" x14ac:dyDescent="0.2">
@@ -16054,13 +16057,13 @@
         <v>998</v>
       </c>
       <c r="D2" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="E2" t="s">
         <v>1004</v>
       </c>
       <c r="F2" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="G2" t="s">
         <v>1037</v>
@@ -16077,16 +16080,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>1425</v>
+        <v>1473</v>
       </c>
       <c r="F3" t="s">
-        <v>1429</v>
+        <v>1474</v>
       </c>
       <c r="G3" s="2">
         <v>45129.574999999997</v>
       </c>
       <c r="H3" t="s">
-        <v>1425</v>
+        <v>1472</v>
       </c>
     </row>
   </sheetData>
@@ -16132,10 +16135,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -16144,7 +16147,7 @@
         <v>45129.574999999997</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21BC53D-678E-4025-83FF-CDE3AB3B08F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611F837F-A240-4D53-8E7A-6B2371590799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4729,10 +4729,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WMT账套01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bksys_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4894,6 +4890,10 @@
   </si>
   <si>
     <t>银行存款-招商银行股份有限公司上海天钥桥支行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沃尔玛全渠道-沃尔玛中国 - Walmart- 财务会计账套001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10799,7 +10799,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D2" t="s">
         <v>1003</v>
@@ -10979,7 +10979,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="D11" t="s">
         <v>1034</v>
@@ -11055,7 +11055,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="F2" s="2">
         <v>45072.29583333333</v>
@@ -11075,7 +11075,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="F3" s="2">
         <v>45072.29583333333</v>
@@ -11095,7 +11095,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="F4" s="2">
         <v>45072.29583333333</v>
@@ -11115,7 +11115,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="F5" s="2">
         <v>45072.29583333333</v>
@@ -11135,7 +11135,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="F6" s="2">
         <v>45072.29583333333</v>
@@ -11155,7 +11155,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="F7" s="2">
         <v>45072.29583333333</v>
@@ -11175,7 +11175,7 @@
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="F8" s="2">
         <v>45072.29583333333</v>
@@ -11195,7 +11195,7 @@
         <v>8</v>
       </c>
       <c r="E9" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="F9" s="2">
         <v>45072.29583333333</v>
@@ -11215,7 +11215,7 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="F10" s="2">
         <v>45072.29583333333</v>
@@ -11235,7 +11235,7 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F11" s="2">
         <v>45072.29583333333</v>
@@ -11255,7 +11255,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F12" s="2">
         <v>45072.29583333333</v>
@@ -11275,7 +11275,7 @@
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="F13" s="2">
         <v>45072.29583333333</v>
@@ -11295,7 +11295,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="F14" s="2">
         <v>45072.29583333333</v>
@@ -11315,7 +11315,7 @@
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="F15" s="2">
         <v>45072.29583333333</v>
@@ -11335,7 +11335,7 @@
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="F16" s="2">
         <v>45072.29583333333</v>
@@ -11355,7 +11355,7 @@
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="F17" s="2">
         <v>45072.29583333333</v>
@@ -11375,7 +11375,7 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F18" s="2">
         <v>45072.29583333333</v>
@@ -11395,7 +11395,7 @@
         <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="F19" s="2">
         <v>45072.29583333333</v>
@@ -11415,7 +11415,7 @@
         <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F20" s="2">
         <v>45072.29583333333</v>
@@ -11435,7 +11435,7 @@
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="F21" s="2">
         <v>45072.29583333333</v>
@@ -11455,7 +11455,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="F22" s="2">
         <v>45072.29583333333</v>
@@ -11475,7 +11475,7 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="F23" s="2">
         <v>45072.29583333333</v>
@@ -11495,7 +11495,7 @@
         <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F24" s="2">
         <v>45072.29583333333</v>
@@ -11515,7 +11515,7 @@
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F25" s="2">
         <v>45072.29583333333</v>
@@ -11535,7 +11535,7 @@
         <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="F26" s="2">
         <v>45072.29583333333</v>
@@ -11555,7 +11555,7 @@
         <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="F27" s="2">
         <v>45072.29583333333</v>
@@ -11575,7 +11575,7 @@
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="F28" s="2">
         <v>45072.29583333333</v>
@@ -11595,7 +11595,7 @@
         <v>8</v>
       </c>
       <c r="E29" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F29" s="2">
         <v>45072.29583333333</v>
@@ -11615,7 +11615,7 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="F30" s="2">
         <v>45072.29583333333</v>
@@ -11635,7 +11635,7 @@
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="F31" s="2">
         <v>45072.29583333333</v>
@@ -11655,7 +11655,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="F32" s="2">
         <v>45072.29583333333</v>
@@ -11675,7 +11675,7 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="F33" s="2">
         <v>45072.29583333333</v>
@@ -11695,7 +11695,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F34" s="2">
         <v>45072.29583333333</v>
@@ -11715,7 +11715,7 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="F35" s="2">
         <v>45072.29583333333</v>
@@ -11735,7 +11735,7 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="F36" s="2">
         <v>45072.29583333333</v>
@@ -11755,7 +11755,7 @@
         <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F37" s="2">
         <v>45072.29583333333</v>
@@ -11775,7 +11775,7 @@
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="F38" s="2">
         <v>45072.29583333333</v>
@@ -11795,7 +11795,7 @@
         <v>8</v>
       </c>
       <c r="E39" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="F39" s="2">
         <v>45072.29583333333</v>
@@ -11815,7 +11815,7 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="F40" s="2">
         <v>45072.29583333333</v>
@@ -11835,7 +11835,7 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="F41" s="2">
         <v>45072.29583333333</v>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>42925.320903603984</v>
+        <v>42390.489956578051</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>44646.255238394704</v>
+        <v>42008.891620971124</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44616.624831157416</v>
+        <v>36436.134809380019</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41011.821786769127</v>
+        <v>35300.38281540756</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38098.65390932891</v>
+        <v>37104.082839239643</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36193.347921871347</v>
+        <v>43731.18728438254</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -12046,7 +12046,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44257.007126525838</v>
+        <v>42992.529548440354</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36976.719584099759</v>
+        <v>43651.718044489702</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39921.452193659759</v>
+        <v>43678.491491414228</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40830.770036896254</v>
+        <v>44227.477806155533</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38374.263447951082</v>
+        <v>43283.611685910022</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37466.687638836469</v>
+        <v>43755.499783475752</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40912.384989805549</v>
+        <v>39460.836752867035</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12221,7 +12221,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40154.501371960832</v>
+        <v>39940.450263810148</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43678.9634574515</v>
+        <v>44342.065132636177</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38181.783900576556</v>
+        <v>41224.685584285726</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43246.25346372513</v>
+        <v>44265.876883702331</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43357.3929326488</v>
+        <v>39552.433266409629</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38100.606110066641</v>
+        <v>39104.062067345716</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36250.83898379976</v>
+        <v>35579.08382985738</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36613.916401759197</v>
+        <v>36074.703374126751</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40784.077867813729</v>
+        <v>43918.223816884129</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37025.142982572172</v>
+        <v>36305.998423735495</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41282.583133026572</v>
+        <v>38860.201691506176</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12496,7 +12496,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38309.801706100443</v>
+        <v>42423.213058199442</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41529.013966300983</v>
+        <v>36072.348056116003</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38834.097447179658</v>
+        <v>38502.059180503471</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35338.158722646665</v>
+        <v>35620.790570681354</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40574.01362182117</v>
+        <v>45063.239518985807</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36675.826620002881</v>
+        <v>43529.148603267553</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -12666,7 +12666,7 @@
         <v>1422</v>
       </c>
       <c r="E2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="F2" t="s">
         <v>1077</v>
@@ -15931,13 +15931,13 @@
         <v>1417</v>
       </c>
       <c r="G2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2" t="s">
         <v>1423</v>
       </c>
       <c r="I2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="3" spans="3:9" x14ac:dyDescent="0.2">
@@ -15948,7 +15948,7 @@
         <v>1002</v>
       </c>
       <c r="E3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="F3">
         <v>200000</v>
@@ -16057,13 +16057,13 @@
         <v>998</v>
       </c>
       <c r="D2" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="E2" t="s">
         <v>1004</v>
       </c>
       <c r="F2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="G2" t="s">
         <v>1037</v>
@@ -16080,16 +16080,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F3" t="s">
         <v>1473</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1474</v>
       </c>
       <c r="G3" s="2">
         <v>45129.574999999997</v>
       </c>
       <c r="H3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
   </sheetData>
@@ -16104,7 +16104,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
@@ -16135,10 +16136,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1424</v>
+        <v>1475</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1424</v>
+        <v>1475</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -16147,7 +16148,7 @@
         <v>45129.574999999997</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1424</v>
+        <v>1475</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611F837F-A240-4D53-8E7A-6B2371590799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B69F4AB-6FA7-418B-BA20-9FCDDFAD2232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_company" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="t_accts" sheetId="6" r:id="rId6"/>
     <sheet name="t_journal" sheetId="8" r:id="rId7"/>
     <sheet name="t_bksys" sheetId="9" r:id="rId8"/>
+    <sheet name="t_policy" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="1476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="1493">
   <si>
     <t>Walmart</t>
   </si>
@@ -4894,6 +4895,74 @@
   </si>
   <si>
     <t>沃尔玛全渠道-沃尔玛中国 - Walmart- 财务会计账套001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>position</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORDER0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LONG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHORT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>order_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLIOCY0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PLIOCY0002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1#策略/普通订单/长头/借/在途物资</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1#策略/普通订单/长头/贷/银行存款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1#策略/普通订单/空头/借/发出商品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1#策略/普通订单/空头/贷/库存商品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2#策略/普通订单/长头/借/在途物资</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2#策略/普通订单/长头/贷/银行存款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2#策略/普通订单/空头/借/应收账款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2#策略/普通订单/空头/贷/主营业务收入 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11896,7 +11965,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>42390.489956578051</v>
+        <v>44271.001013447203</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11921,7 +11990,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>42008.891620971124</v>
+        <v>42645.13109735772</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -11946,7 +12015,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36436.134809380019</v>
+        <v>37460.852678978685</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -11971,7 +12040,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35300.38281540756</v>
+        <v>43088.722294846535</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -11996,7 +12065,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37104.082839239643</v>
+        <v>42129.967910967534</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -12021,7 +12090,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43731.18728438254</v>
+        <v>44120.059687564157</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -12046,7 +12115,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42992.529548440354</v>
+        <v>36058.29846607428</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -12071,7 +12140,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43651.718044489702</v>
+        <v>35643.236492486642</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -12096,7 +12165,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43678.491491414228</v>
+        <v>35484.090310247346</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12121,7 +12190,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44227.477806155533</v>
+        <v>41306.992315892589</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12146,7 +12215,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43283.611685910022</v>
+        <v>43701.241855912478</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12171,7 +12240,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43755.499783475752</v>
+        <v>40983.713667053722</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12196,7 +12265,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39460.836752867035</v>
+        <v>44271.091847125346</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12221,7 +12290,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39940.450263810148</v>
+        <v>41467.596341738928</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12246,7 +12315,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44342.065132636177</v>
+        <v>36306.746921537939</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12271,7 +12340,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41224.685584285726</v>
+        <v>43153.536405544073</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12296,7 +12365,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44265.876883702331</v>
+        <v>41410.063595316838</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12321,7 +12390,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39552.433266409629</v>
+        <v>38640.455483193138</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12346,7 +12415,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39104.062067345716</v>
+        <v>38947.916548205692</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12371,7 +12440,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35579.08382985738</v>
+        <v>44170.800386582749</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12396,7 +12465,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36074.703374126751</v>
+        <v>35779.023864846196</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12421,7 +12490,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43918.223816884129</v>
+        <v>39622.855615627552</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12446,7 +12515,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36305.998423735495</v>
+        <v>36236.914091384861</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12471,7 +12540,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38860.201691506176</v>
+        <v>40119.313771779467</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12496,7 +12565,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42423.213058199442</v>
+        <v>40081.592088375153</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12521,7 +12590,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36072.348056116003</v>
+        <v>37291.920251812102</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12546,7 +12615,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38502.059180503471</v>
+        <v>40770.838304173194</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12571,7 +12640,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35620.790570681354</v>
+        <v>43200.584505962557</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12596,7 +12665,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>45063.239518985807</v>
+        <v>43102.359258308352</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12621,7 +12690,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43529.148603267553</v>
+        <v>39813.307770997664</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -16155,4 +16224,230 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BAB75F4-CF88-4683-9DC4-6FEC4CE23155}">
+  <dimension ref="C2:I10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>998</v>
+      </c>
+      <c r="D2" t="s">
+        <v>999</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="3" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H3">
+        <v>1402</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H4">
+        <v>1002</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H5">
+        <v>1407</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H6">
+        <v>1406</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H7">
+        <v>1402</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H8">
+        <v>1002</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H9">
+        <v>1122</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H10">
+        <v>6001</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B69F4AB-6FA7-418B-BA20-9FCDDFAD2232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F915DABE-B574-4A52-9C05-3D0DCC75A9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="t_accts" sheetId="6" r:id="rId6"/>
     <sheet name="t_journal" sheetId="8" r:id="rId7"/>
     <sheet name="t_bksys" sheetId="9" r:id="rId8"/>
-    <sheet name="t_policy" sheetId="10" r:id="rId9"/>
+    <sheet name="t_acct_policy" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>44271.001013447203</v>
+        <v>43103.905662500911</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>42645.13109735772</v>
+        <v>36668.431736741382</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37460.852678978685</v>
+        <v>37572.595778477218</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43088.722294846535</v>
+        <v>42482.524079128809</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42129.967910967534</v>
+        <v>38593.148786827813</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44120.059687564157</v>
+        <v>43586.588792708768</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -12115,7 +12115,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36058.29846607428</v>
+        <v>44027.795358439376</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35643.236492486642</v>
+        <v>42854.143359283044</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35484.090310247346</v>
+        <v>37405.875853988073</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41306.992315892589</v>
+        <v>42178.604946137973</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43701.241855912478</v>
+        <v>43369.36425133083</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40983.713667053722</v>
+        <v>42718.361013819842</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44271.091847125346</v>
+        <v>35628.619189787045</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12290,7 +12290,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41467.596341738928</v>
+        <v>44277.337814184662</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12315,7 +12315,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36306.746921537939</v>
+        <v>40492.070982252917</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43153.536405544073</v>
+        <v>40922.576131944319</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41410.063595316838</v>
+        <v>44595.944214335032</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38640.455483193138</v>
+        <v>44129.422107634207</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38947.916548205692</v>
+        <v>41573.49260402564</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44170.800386582749</v>
+        <v>39424.877474947454</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35779.023864846196</v>
+        <v>45131.218729096421</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12490,7 +12490,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39622.855615627552</v>
+        <v>38430.353904393865</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12515,7 +12515,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36236.914091384861</v>
+        <v>36264.800484851417</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40119.313771779467</v>
+        <v>39382.424407440478</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40081.592088375153</v>
+        <v>39248.788912418648</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37291.920251812102</v>
+        <v>38717.930934425072</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40770.838304173194</v>
+        <v>39515.433063071941</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43200.584505962557</v>
+        <v>39181.697080462291</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43102.359258308352</v>
+        <v>38504.253434007114</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12690,7 +12690,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39813.307770997664</v>
+        <v>42766.075121475282</v>
       </c>
       <c r="F32">
         <v>123456</v>

--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F915DABE-B574-4A52-9C05-3D0DCC75A9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2586E38B-7CA1-4F95-9340-AF3E04EC106B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4926,14 +4926,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PLIOCY0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PLIOCY0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1#策略/普通订单/长头/借/在途物资</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4964,6 +4956,12 @@
   <si>
     <t xml:space="preserve">2#策略/普通订单/空头/贷/主营业务收入 </t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POLICY0001</t>
+  </si>
+  <si>
+    <t>POLICY0002</t>
   </si>
 </sst>
 </file>
@@ -11965,7 +11963,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>43103.905662500911</v>
+        <v>35614.386878160651</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11990,7 +11988,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>36668.431736741382</v>
+        <v>43064.84428289222</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -12015,7 +12013,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37572.595778477218</v>
+        <v>35626.032122609395</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -12040,7 +12038,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42482.524079128809</v>
+        <v>44232.642630478003</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -12065,7 +12063,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38593.148786827813</v>
+        <v>39431.528603665975</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -12090,7 +12088,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43586.588792708768</v>
+        <v>35607.080006210192</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -12115,7 +12113,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44027.795358439376</v>
+        <v>38285.136936225914</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -12140,7 +12138,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42854.143359283044</v>
+        <v>40009.045460693087</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -12165,7 +12163,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37405.875853988073</v>
+        <v>39104.167862578426</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12190,7 +12188,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42178.604946137973</v>
+        <v>39381.169854345811</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12215,7 +12213,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43369.36425133083</v>
+        <v>40431.76103438103</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12240,7 +12238,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42718.361013819842</v>
+        <v>39443.203211602762</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12265,7 +12263,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35628.619189787045</v>
+        <v>40320.424612275048</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12290,7 +12288,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44277.337814184662</v>
+        <v>39314.833025707798</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12315,7 +12313,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40492.070982252917</v>
+        <v>38655.602521458975</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12340,7 +12338,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40922.576131944319</v>
+        <v>36562.262714995217</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12365,7 +12363,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44595.944214335032</v>
+        <v>42083.007451238402</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12390,7 +12388,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44129.422107634207</v>
+        <v>44776.150352354824</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12415,7 +12413,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41573.49260402564</v>
+        <v>36429.897855428084</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12440,7 +12438,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39424.877474947454</v>
+        <v>44621.015573874363</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12465,7 +12463,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>45131.218729096421</v>
+        <v>36444.631604902366</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12490,7 +12488,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38430.353904393865</v>
+        <v>41263.057809494152</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12515,7 +12513,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36264.800484851417</v>
+        <v>35632.164298537646</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12540,7 +12538,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39382.424407440478</v>
+        <v>39852.077280668644</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12565,7 +12563,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39248.788912418648</v>
+        <v>38800.545819754618</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12590,7 +12588,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38717.930934425072</v>
+        <v>40977.090390916244</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12615,7 +12613,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39515.433063071941</v>
+        <v>43962.843438589254</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12640,7 +12638,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39181.697080462291</v>
+        <v>40904.167702806626</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12665,7 +12663,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38504.253434007114</v>
+        <v>41670.529145283988</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12690,7 +12688,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42766.075121475282</v>
+        <v>40516.46659743652</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -16267,7 +16265,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
       <c r="E3" t="s">
         <v>1477</v>
@@ -16282,7 +16280,7 @@
         <v>1402</v>
       </c>
       <c r="I3" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.2">
@@ -16290,7 +16288,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
       <c r="E4" t="s">
         <v>1477</v>
@@ -16305,7 +16303,7 @@
         <v>1002</v>
       </c>
       <c r="I4" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.2">
@@ -16313,7 +16311,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
       <c r="E5" t="s">
         <v>1477</v>
@@ -16328,7 +16326,7 @@
         <v>1407</v>
       </c>
       <c r="I5" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.2">
@@ -16336,7 +16334,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
       <c r="E6" t="s">
         <v>1477</v>
@@ -16351,7 +16349,7 @@
         <v>1406</v>
       </c>
       <c r="I6" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.2">
@@ -16359,7 +16357,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
       <c r="E7" t="s">
         <v>1477</v>
@@ -16374,7 +16372,7 @@
         <v>1402</v>
       </c>
       <c r="I7" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.2">
@@ -16382,7 +16380,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
       <c r="E8" t="s">
         <v>1477</v>
@@ -16397,7 +16395,7 @@
         <v>1002</v>
       </c>
       <c r="I8" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.2">
@@ -16405,7 +16403,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
       <c r="E9" t="s">
         <v>1477</v>
@@ -16420,7 +16418,7 @@
         <v>1122</v>
       </c>
       <c r="I9" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.2">
@@ -16428,7 +16426,7 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
       <c r="E10" t="s">
         <v>1477</v>
@@ -16443,7 +16441,7 @@
         <v>6001</v>
       </c>
       <c r="I10" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2586E38B-7CA1-4F95-9340-AF3E04EC106B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B035A43C-ECA4-406A-8551-0934556E0B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4902,10 +4902,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ORDER0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LONG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4922,10 +4918,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>order_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1#策略/普通订单/长头/借/在途物资</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4962,6 +4954,13 @@
   </si>
   <si>
     <t>POLICY0002</t>
+  </si>
+  <si>
+    <t>bill_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BILL0001</t>
   </si>
 </sst>
 </file>
@@ -11963,7 +11962,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>35614.386878160651</v>
+        <v>43442.443413355271</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11988,7 +11987,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>43064.84428289222</v>
+        <v>43040.516666882933</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -12013,7 +12012,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35626.032122609395</v>
+        <v>41835.137584916476</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -12038,7 +12037,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44232.642630478003</v>
+        <v>43814.784447432474</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -12063,7 +12062,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39431.528603665975</v>
+        <v>40199.74604582334</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -12088,7 +12087,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35607.080006210192</v>
+        <v>44606.876591751963</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -12113,7 +12112,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38285.136936225914</v>
+        <v>45293.149000773417</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -12138,7 +12137,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40009.045460693087</v>
+        <v>40227.34515780479</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -12163,7 +12162,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39104.167862578426</v>
+        <v>40241.146817068133</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12188,7 +12187,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39381.169854345811</v>
+        <v>44826.333320419668</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12213,7 +12212,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40431.76103438103</v>
+        <v>39638.13382895424</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12238,7 +12237,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39443.203211602762</v>
+        <v>35609.296313982049</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12263,7 +12262,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40320.424612275048</v>
+        <v>44993.750245400413</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12288,7 +12287,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39314.833025707798</v>
+        <v>40610.358260417255</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12313,7 +12312,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38655.602521458975</v>
+        <v>40341.630773995115</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12338,7 +12337,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36562.262714995217</v>
+        <v>36405.275954196906</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12363,7 +12362,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42083.007451238402</v>
+        <v>41281.650775228656</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12388,7 +12387,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44776.150352354824</v>
+        <v>43805.323475640609</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12413,7 +12412,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36429.897855428084</v>
+        <v>37587.11771639045</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12438,7 +12437,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44621.015573874363</v>
+        <v>44644.211800742378</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12463,7 +12462,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36444.631604902366</v>
+        <v>43541.979676441202</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12488,7 +12487,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41263.057809494152</v>
+        <v>38487.666750990713</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12513,7 +12512,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35632.164298537646</v>
+        <v>36046.387695286183</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12538,7 +12537,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39852.077280668644</v>
+        <v>35895.966477215174</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12563,7 +12562,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38800.545819754618</v>
+        <v>36441.566057108394</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12588,7 +12587,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40977.090390916244</v>
+        <v>38597.222241431402</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12613,7 +12612,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43962.843438589254</v>
+        <v>40313.238707876888</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12638,7 +12637,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40904.167702806626</v>
+        <v>41133.167437830605</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12663,7 +12662,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41670.529145283988</v>
+        <v>37724.011659894342</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12688,7 +12687,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40516.46659743652</v>
+        <v>43753.353861121504</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -16245,7 +16244,7 @@
         <v>999</v>
       </c>
       <c r="E2" t="s">
-        <v>1482</v>
+        <v>1491</v>
       </c>
       <c r="F2" t="s">
         <v>1476</v>
@@ -16265,22 +16264,22 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="E3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F3" t="s">
         <v>1477</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>1478</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1479</v>
       </c>
       <c r="H3">
         <v>1402</v>
       </c>
       <c r="I3" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.2">
@@ -16288,22 +16287,22 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="E4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F4" t="s">
         <v>1477</v>
       </c>
-      <c r="F4" t="s">
-        <v>1478</v>
-      </c>
       <c r="G4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H4">
         <v>1002</v>
       </c>
       <c r="I4" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.2">
@@ -16311,22 +16310,22 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="E5" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="F5" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G5" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H5">
         <v>1407</v>
       </c>
       <c r="I5" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.2">
@@ -16334,22 +16333,22 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="E6" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="F6" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G6" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H6">
         <v>1406</v>
       </c>
       <c r="I6" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.2">
@@ -16357,22 +16356,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E7" t="s">
         <v>1492</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>1477</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>1478</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1479</v>
       </c>
       <c r="H7">
         <v>1402</v>
       </c>
       <c r="I7" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.2">
@@ -16380,22 +16379,22 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E8" t="s">
         <v>1492</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>1477</v>
       </c>
-      <c r="F8" t="s">
-        <v>1478</v>
-      </c>
       <c r="G8" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H8">
         <v>1002</v>
       </c>
       <c r="I8" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.2">
@@ -16403,22 +16402,22 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E9" t="s">
         <v>1492</v>
       </c>
-      <c r="E9" t="s">
-        <v>1477</v>
-      </c>
       <c r="F9" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G9" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H9">
         <v>1122</v>
       </c>
       <c r="I9" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.2">
@@ -16426,22 +16425,22 @@
         <v>8</v>
       </c>
       <c r="D10" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E10" t="s">
         <v>1492</v>
       </c>
-      <c r="E10" t="s">
-        <v>1477</v>
-      </c>
       <c r="F10" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G10" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H10">
         <v>6001</v>
       </c>
       <c r="I10" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/java/gbench/sandbox/data/datafile.xlsx
+++ b/src/test/java/gbench/sandbox/data/datafile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B035A43C-ECA4-406A-8551-0934556E0B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9818DABB-BF6B-4752-903D-AB22E07A0EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_company" sheetId="1" r:id="rId1"/>
@@ -5012,11 +5012,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11962,7 +11963,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>43442.443413355271</v>
+        <v>35441.708330866299</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -11987,7 +11988,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>43040.516666882933</v>
+        <v>44661.666016369258</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -12012,7 +12013,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41835.137584916476</v>
+        <v>43792.289515323639</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -12037,7 +12038,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43814.784447432474</v>
+        <v>35602.064171841121</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -12062,7 +12063,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40199.74604582334</v>
+        <v>40697.810823220861</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -12087,7 +12088,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44606.876591751963</v>
+        <v>39262.497084104471</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -12112,7 +12113,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>45293.149000773417</v>
+        <v>42685.840867824438</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -12137,7 +12138,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40227.34515780479</v>
+        <v>41489.25749925767</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -12162,7 +12163,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40241.146817068133</v>
+        <v>40716.041264267158</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -12187,7 +12188,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44826.333320419668</v>
+        <v>35689.172133907836</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -12212,7 +12213,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39638.13382895424</v>
+        <v>40587.585529301825</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -12237,7 +12238,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35609.296313982049</v>
+        <v>38814.013595959404</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -12262,7 +12263,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44993.750245400413</v>
+        <v>43214.145416499705</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -12287,7 +12288,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40610.358260417255</v>
+        <v>40317.570800056434</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -12312,7 +12313,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40341.630773995115</v>
+        <v>44677.071820334975</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -12337,7 +12338,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36405.275954196906</v>
+        <v>35421.231698257383</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -12362,7 +12363,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41281.650775228656</v>
+        <v>44721.610117732351</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -12387,7 +12388,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43805.323475640609</v>
+        <v>40584.447251425168</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -12412,7 +12413,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37587.11771639045</v>
+        <v>42160.409261044391</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -12437,7 +12438,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44644.211800742378</v>
+        <v>39166.230375482941</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -12462,7 +12463,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43541.979676441202</v>
+        <v>36310.635339202563</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -12487,7 +12488,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38487.666750990713</v>
+        <v>36611.041253030809</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -12512,7 +12513,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36046.387695286183</v>
+        <v>43530.405786036717</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -12537,7 +12538,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35895.966477215174</v>
+        <v>39602.44606573748</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -12562,7 +12563,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36441.566057108394</v>
+        <v>44028.317597886118</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -12587,7 +12588,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38597.222241431402</v>
+        <v>38131.031357451873</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -12612,7 +12613,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40313.238707876888</v>
+        <v>43835.727499162211</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -12637,7 +12638,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41133.167437830605</v>
+        <v>37108.747341061768</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -12662,7 +12663,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37724.011659894342</v>
+        <v>40398.81225466379</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -12687,7 +12688,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43753.353861121504</v>
+        <v>37520.469343045392</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -15978,7 +15979,7 @@
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="45.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
   </cols>
@@ -16016,8 +16017,8 @@
       <c r="E3" t="s">
         <v>1474</v>
       </c>
-      <c r="F3">
-        <v>200000</v>
+      <c r="F3" s="4">
+        <v>200000.03</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -16039,8 +16040,8 @@
       <c r="E4" t="s">
         <v>1418</v>
       </c>
-      <c r="F4">
-        <v>100000</v>
+      <c r="F4" s="4">
+        <v>100000.01</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -16062,8 +16063,8 @@
       <c r="E5" t="s">
         <v>1419</v>
       </c>
-      <c r="F5">
-        <v>60000</v>
+      <c r="F5" s="4">
+        <v>60000.01</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -16085,8 +16086,8 @@
       <c r="E6" t="s">
         <v>1420</v>
       </c>
-      <c r="F6">
-        <v>40000</v>
+      <c r="F6" s="4">
+        <v>40000.01</v>
       </c>
       <c r="G6">
         <v>-1</v>
